--- a/ai_logs/Nguyên_AI_Log.xlsx
+++ b/ai_logs/Nguyên_AI_Log.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\SUM26\labl\Food_delivery\ai_logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD084692-344D-41A6-B75D-B9D0145DEA0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36A46E31-21E6-4F4C-AB66-647379E9C4BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -468,18 +468,12 @@
     <t>✅</t>
   </si>
   <si>
-    <t>Entries 004-007: mỗi prompt đều dẫn đến thay đổi schema DB, logic data generator, hoặc kiến trúc import pipeline</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
     <t>Nếu không có prompt này, project có thay đổi về architecture/design?</t>
   </si>
   <si>
-    <t>004 → đổi toàn bộ DDL sang T-SQL; 006 → đổi cách encode địa chỉ CSV; 007 → refactor data generator</t>
-  </si>
-  <si>
     <t>3</t>
   </si>
   <si>
@@ -495,9 +489,6 @@
     <t>Có minh chứng cụ thể (code, metrics, comparison)?</t>
   </si>
   <si>
-    <t>004: lỗi Msg 102 screenshot; 005: CSV diff hash; 006: Msg 4864 + code fix; 007: SQL query 0 rows</t>
-  </si>
-  <si>
     <t>5</t>
   </si>
   <si>
@@ -516,15 +507,9 @@
     <t>Số lượng entries nằm trong range (min-max)?</t>
   </si>
   <si>
-    <t>7 entries (004-007 từ Gemini session + 001-003 từ template). Tổng hợp hợp lệ.</t>
-  </si>
-  <si>
     <t>Mỗi DTC component có ít nhất 1 core prompt?</t>
   </si>
   <si>
-    <t>Decomposition ✓ (004), Pattern Recognition ✓ (006), Abstraction ✓ (007), Algorithms ✓ (005)</t>
-  </si>
-  <si>
     <t>Đã phát hiện ≥ số lượng hallucination yêu cầu?</t>
   </si>
   <si>
@@ -628,6 +613,21 @@
   </si>
   <si>
     <t>high</t>
+  </si>
+  <si>
+    <t>Entries 001-004: mỗi prompt đều dẫn đến thay đổi schema DB, logic data generator, hoặc kiến trúc import pipeline</t>
+  </si>
+  <si>
+    <t>001 → đổi toàn bộ DDL sang T-SQL; 003 → đổi cách encode địa chỉ CSV; 004 → refactor data generator</t>
+  </si>
+  <si>
+    <t>001: lỗi Msg 102 screenshot; 002: CSV diff hash; 006: Msg 4864 + code fix; 004: SQL query 0 rows</t>
+  </si>
+  <si>
+    <t>4 entries (001-004) từ Gemini session + 001-003 từ template). Tổng hợp hợp lệ.</t>
+  </si>
+  <si>
+    <t>Decomposition ✓ (001), Pattern Recognition ✓ (003), Abstraction ✓ (004), Algorithms ✓ (002)</t>
   </si>
 </sst>
 </file>
@@ -637,7 +637,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -749,6 +749,19 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="12">
@@ -938,15 +951,9 @@
     <xf numFmtId="0" fontId="17" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -959,13 +966,22 @@
     <xf numFmtId="0" fontId="19" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -975,19 +991,16 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1303,14 +1316,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
     </row>
     <row r="3" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -1472,8 +1485,8 @@
       <c r="B21" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C21" s="47" t="s">
-        <v>197</v>
+      <c r="C21" s="18" t="s">
+        <v>192</v>
       </c>
       <c r="D21" t="s">
         <v>78</v>
@@ -1562,28 +1575,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
     </row>
     <row r="3" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
@@ -1612,7 +1625,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="109.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="37" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="20" t="s">
@@ -1633,12 +1646,12 @@
       <c r="G4" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="22" t="s">
+      <c r="H4" s="47" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="109.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="46" t="s">
+      <c r="A5" s="37" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="23" t="s">
@@ -1664,7 +1677,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="109.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="46" t="s">
+      <c r="A6" s="37" t="s">
         <v>16</v>
       </c>
       <c r="B6" s="23" t="s">
@@ -1690,7 +1703,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="109.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="46" t="s">
+      <c r="A7" s="37" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="28" t="s">
@@ -1890,29 +1903,29 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="22" style="46" customWidth="1"/>
     <col min="3" max="6" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="42" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
     </row>
     <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
@@ -1935,10 +1948,10 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="43" t="s">
+      <c r="A4" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="9" t="s">
         <v>93</v>
       </c>
       <c r="C4" s="7" t="s">
@@ -1955,10 +1968,10 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="26" t="s">
         <v>98</v>
       </c>
       <c r="C5" s="27" t="s">
@@ -1975,30 +1988,30 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="45" t="s">
+      <c r="A6" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="45" t="s">
         <v>103</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="D6" s="33" t="s">
+      <c r="D6" s="31" t="s">
         <v>105</v>
       </c>
-      <c r="E6" s="33" t="s">
+      <c r="E6" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="F6" s="33" t="s">
+      <c r="F6" s="31" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="44" t="s">
+      <c r="A7" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="26" t="s">
         <v>98</v>
       </c>
       <c r="C7" s="27" t="s">
@@ -2016,7 +2029,7 @@
     </row>
     <row r="8" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
+      <c r="B8" s="9"/>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
@@ -2024,7 +2037,7 @@
     </row>
     <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
+      <c r="B9" s="9"/>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
@@ -2032,7 +2045,7 @@
     </row>
     <row r="10" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
+      <c r="B10" s="9"/>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
@@ -2040,7 +2053,7 @@
     </row>
     <row r="11" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
+      <c r="B11" s="9"/>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
@@ -2048,7 +2061,7 @@
     </row>
     <row r="12" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
+      <c r="B12" s="9"/>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
@@ -2056,7 +2069,7 @@
     </row>
     <row r="13" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
+      <c r="B13" s="9"/>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
@@ -2064,7 +2077,7 @@
     </row>
     <row r="14" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
+      <c r="B14" s="9"/>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
@@ -2072,7 +2085,7 @@
     </row>
     <row r="15" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
+      <c r="B15" s="9"/>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
@@ -2080,7 +2093,7 @@
     </row>
     <row r="16" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
+      <c r="B16" s="9"/>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
@@ -2088,7 +2101,7 @@
     </row>
     <row r="17" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
+      <c r="B17" s="9"/>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
@@ -2096,7 +2109,7 @@
     </row>
     <row r="18" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
+      <c r="B18" s="9"/>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
@@ -2104,7 +2117,7 @@
     </row>
     <row r="19" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
+      <c r="B19" s="9"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
@@ -2112,7 +2125,7 @@
     </row>
     <row r="20" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
+      <c r="B20" s="9"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
@@ -2120,7 +2133,7 @@
     </row>
     <row r="21" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
+      <c r="B21" s="9"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
@@ -2128,7 +2141,7 @@
     </row>
     <row r="22" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
+      <c r="B22" s="9"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
@@ -2136,7 +2149,7 @@
     </row>
     <row r="23" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
+      <c r="B23" s="9"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
@@ -2144,7 +2157,7 @@
     </row>
     <row r="24" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
+      <c r="B24" s="9"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
@@ -2152,7 +2165,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
+      <c r="B25" s="9"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
@@ -2160,7 +2173,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
+      <c r="B26" s="9"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
@@ -2168,7 +2181,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
+      <c r="B27" s="9"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
@@ -2185,7 +2198,7 @@
       <c r="A34" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="17" t="s">
         <v>114</v>
       </c>
       <c r="C34" s="10" t="s">
@@ -2196,7 +2209,7 @@
       <c r="A35" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="B35" s="7" t="s">
+      <c r="B35" s="9" t="s">
         <v>116</v>
       </c>
       <c r="C35" s="7" t="s">
@@ -2207,7 +2220,7 @@
       <c r="A36" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B36" s="7" t="s">
+      <c r="B36" s="9" t="s">
         <v>118</v>
       </c>
       <c r="C36" s="7" t="s">
@@ -2218,7 +2231,7 @@
       <c r="A37" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="B37" s="7" t="s">
+      <c r="B37" s="9" t="s">
         <v>120</v>
       </c>
       <c r="C37" s="7" t="s">
@@ -2229,7 +2242,7 @@
       <c r="A38" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B38" s="9" t="s">
         <v>123</v>
       </c>
       <c r="C38" s="7" t="s">
@@ -2240,7 +2253,7 @@
       <c r="A39" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="B39" s="7" t="s">
+      <c r="B39" s="9" t="s">
         <v>126</v>
       </c>
       <c r="C39" s="7" t="s">
@@ -2251,7 +2264,7 @@
       <c r="A40" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="B40" s="30" t="s">
+      <c r="B40" s="26" t="s">
         <v>98</v>
       </c>
       <c r="C40" s="27" t="s">
@@ -2268,22 +2281,22 @@
       </c>
     </row>
     <row r="41" spans="1:6" ht="57" x14ac:dyDescent="0.3">
-      <c r="A41" s="31" t="s">
+      <c r="A41" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="B41" s="32" t="s">
+      <c r="B41" s="45" t="s">
         <v>103</v>
       </c>
-      <c r="C41" s="33" t="s">
+      <c r="C41" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="D41" s="33" t="s">
+      <c r="D41" s="31" t="s">
         <v>129</v>
       </c>
-      <c r="E41" s="33" t="s">
+      <c r="E41" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="F41" s="33" t="s">
+      <c r="F41" s="31" t="s">
         <v>107</v>
       </c>
     </row>
@@ -2291,7 +2304,7 @@
       <c r="A42" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="30" t="s">
+      <c r="B42" s="26" t="s">
         <v>98</v>
       </c>
       <c r="C42" s="27" t="s">
@@ -2326,20 +2339,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="38" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="43" t="s">
         <v>135</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -2367,72 +2380,72 @@
       <c r="B6" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="C6" s="34" t="s">
+      <c r="C6" s="32" t="s">
         <v>143</v>
       </c>
-      <c r="D6" s="35" t="s">
-        <v>144</v>
+      <c r="D6" s="33" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" s="32" t="s">
         <v>143</v>
       </c>
-      <c r="D7" s="35" t="s">
-        <v>147</v>
+      <c r="D7" s="33" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>143</v>
+      </c>
+      <c r="D8" s="33" t="s">
         <v>148</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="C8" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="D8" s="35" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="C9" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="C9" s="32" t="s">
         <v>143</v>
       </c>
-      <c r="D9" s="35" t="s">
-        <v>153</v>
+      <c r="D9" s="33" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="C10" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="C10" s="32" t="s">
         <v>143</v>
       </c>
-      <c r="D10" s="35" t="s">
-        <v>156</v>
+      <c r="D10" s="33" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -2446,7 +2459,7 @@
         <v>139</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="22.8" x14ac:dyDescent="0.3">
@@ -2454,94 +2467,94 @@
         <v>141</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="C14" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="C14" s="32" t="s">
         <v>143</v>
       </c>
-      <c r="D14" s="35" t="s">
-        <v>160</v>
+      <c r="D14" s="33" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="C15" s="34" t="s">
+        <v>157</v>
+      </c>
+      <c r="C15" s="32" t="s">
         <v>143</v>
       </c>
-      <c r="D15" s="35" t="s">
-        <v>162</v>
+      <c r="D15" s="33" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="C16" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="C16" s="32" t="s">
         <v>143</v>
       </c>
-      <c r="D16" s="35" t="s">
-        <v>164</v>
+      <c r="D16" s="33" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="C17" s="34" t="s">
+        <v>160</v>
+      </c>
+      <c r="C17" s="32" t="s">
         <v>143</v>
       </c>
-      <c r="D17" s="35" t="s">
-        <v>166</v>
+      <c r="D17" s="33" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="C18" s="34" t="s">
+        <v>162</v>
+      </c>
+      <c r="C18" s="32" t="s">
         <v>143</v>
       </c>
-      <c r="D18" s="35" t="s">
-        <v>168</v>
+      <c r="D18" s="33" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2549,111 +2562,111 @@
         <v>2</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B28" s="36" t="s">
-        <v>177</v>
-      </c>
-      <c r="C28" s="36" t="s">
-        <v>178</v>
-      </c>
-      <c r="D28" s="35" t="s">
-        <v>196</v>
+      <c r="B28" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="C28" s="34" t="s">
+        <v>173</v>
+      </c>
+      <c r="D28" s="33" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B29" s="36" t="s">
-        <v>179</v>
-      </c>
-      <c r="C29" s="36" t="s">
-        <v>180</v>
-      </c>
-      <c r="D29" s="35" t="s">
-        <v>181</v>
+      <c r="B29" s="34" t="s">
+        <v>174</v>
+      </c>
+      <c r="C29" s="34" t="s">
+        <v>175</v>
+      </c>
+      <c r="D29" s="33" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="B30" s="36" t="s">
-        <v>182</v>
-      </c>
-      <c r="C30" s="36" t="s">
-        <v>183</v>
-      </c>
-      <c r="D30" s="35" t="s">
-        <v>196</v>
+      <c r="B30" s="34" t="s">
+        <v>177</v>
+      </c>
+      <c r="C30" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="D30" s="33" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="B31" s="36" t="s">
-        <v>184</v>
-      </c>
-      <c r="C31" s="36" t="s">
-        <v>185</v>
-      </c>
-      <c r="D31" s="35" t="s">
-        <v>186</v>
+      <c r="B31" s="34" t="s">
+        <v>179</v>
+      </c>
+      <c r="C31" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="D31" s="33" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B32" s="36" t="s">
-        <v>187</v>
-      </c>
-      <c r="C32" s="36" t="s">
-        <v>188</v>
-      </c>
-      <c r="D32" s="35" t="s">
-        <v>189</v>
+      <c r="B32" s="34" t="s">
+        <v>182</v>
+      </c>
+      <c r="C32" s="34" t="s">
+        <v>183</v>
+      </c>
+      <c r="D32" s="33" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="B33" s="36" t="s">
-        <v>190</v>
-      </c>
-      <c r="C33" s="36" t="s">
-        <v>191</v>
-      </c>
-      <c r="D33" s="35" t="s">
-        <v>192</v>
+      <c r="B33" s="34" t="s">
+        <v>185</v>
+      </c>
+      <c r="C33" s="34" t="s">
+        <v>186</v>
+      </c>
+      <c r="D33" s="33" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="36" t="s">
-        <v>193</v>
-      </c>
-      <c r="C34" s="36" t="s">
-        <v>194</v>
-      </c>
-      <c r="D34" s="35" t="s">
-        <v>195</v>
+      <c r="B34" s="34" t="s">
+        <v>188</v>
+      </c>
+      <c r="C34" s="34" t="s">
+        <v>189</v>
+      </c>
+      <c r="D34" s="33" t="s">
+        <v>190</v>
       </c>
     </row>
   </sheetData>

--- a/ai_logs/Nguyên_AI_Log.xlsx
+++ b/ai_logs/Nguyên_AI_Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\SUM26\labl\Food_delivery\ai_logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36A46E31-21E6-4F4C-AB66-647379E9C4BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E583E022-5924-40B2-B326-1A7E1BD061D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="223">
   <si>
     <t>DETAILED AI AUDIT LOG</t>
   </si>
@@ -318,18 +318,6 @@
     <t>Fabrication</t>
   </si>
   <si>
-    <t>Paper 'Smith et al. 2023' exists</t>
-  </si>
-  <si>
-    <t>Paper NOT FOUND on Google Scholar</t>
-  </si>
-  <si>
-    <t>Searched Google Scholar, ResearchGate</t>
-  </si>
-  <si>
-    <t>Used real paper 'Jones et al. 2022'</t>
-  </si>
-  <si>
     <t>Logic Error</t>
   </si>
   <si>
@@ -495,9 +483,6 @@
     <t>Prompt này phản ánh tư duy phản biện, không chỉ copy AI?</t>
   </si>
   <si>
-    <t>Mỗi entry đều phản bác hoặc sửa đổi gợi ý của AI, không copy-paste nguyên xi</t>
-  </si>
-  <si>
     <t>B. KIỂM TRA TỔNG THỂ LOG</t>
   </si>
   <si>
@@ -621,13 +606,115 @@
     <t>001 → đổi toàn bộ DDL sang T-SQL; 003 → đổi cách encode địa chỉ CSV; 004 → refactor data generator</t>
   </si>
   <si>
-    <t>001: lỗi Msg 102 screenshot; 002: CSV diff hash; 006: Msg 4864 + code fix; 004: SQL query 0 rows</t>
-  </si>
-  <si>
     <t>4 entries (001-004) từ Gemini session + 001-003 từ template). Tổng hợp hợp lệ.</t>
   </si>
   <si>
     <t>Decomposition ✓ (001), Pattern Recognition ✓ (003), Abstraction ✓ (004), Algorithms ✓ (002)</t>
+  </si>
+  <si>
+    <t>JUnit test OrderContentionJUnitTest chạy thành công nhưng chưa in kết quả ra màn hình — không thể quan sát được luồng nào thắng tranh chấp Optimistic Locking và tổng số OptimisticLockException được ném ra trong suốt quá trình test.</t>
+  </si>
+  <si>
+    <t>"test chạy đc nhưng muốn in ra màn hình kết quả chạy thì làm ntn" (kèm code OrderContentionJUnitTest.java và OrderRepository.java)</t>
+  </si>
+  <si>
+    <t>AI đọc code, xác định test đang có 5 driver tranh 1 order nhưng biến numOrders chưa được dùng. Đề xuất thêm System.out.println() tại 3 điểm: (1) trước latch.await() để confirm driver sẵn sàng, (2) ngay sau khi gán đơn thành công với tag [SUCCESS], (3) khi bắt OptimisticLockException với tag [FAILED]. Thêm bảng tổng kết sau awaitTermination() in: tổng tài xế, số thành công, số OptimisticLock, số lỗi khác. Thêm vòng for in chi tiết từng Order sau assertEquals.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: AI viết lại method test với biến 'numOrders = 5' nhưng vòng setUp() vẫn chỉ tạo 1 đơn hàng trong file CSV — mâu thuẫn giữa numOrders khai báo và dữ liệu thực tế sẽ khiến findById(2..5) luôn trả về null và bảng in cuối cùng bị thiếu dòng, hoặc gây NullPointerException khi assert.
+Contextualization: Mục tiêu lúc này chỉ là quan sát output của test 5-driver-vs-1-order đang hoạt động đúng — không cần mở rộng numOrders ngay.
+Creative Synthesis: Chỉ lấy phần System.out.println() từ code AI đề xuất, bỏ phần thay đổi numOrders và vòng for in 5 order (vì CSV chỉ có 1 order). Giữ assertEquals(1, successCount) và assertEquals(4, exceptionCount) nguyên bản.
+Decision: Thêm logging vào đúng 3 điểm AI chỉ ra, giữ nguyên cấu trúc test ban đầu, không mở rộng sang multi-order ở bước này.</t>
+  </si>
+  <si>
+    <t>Console output sau khi thêm println: [SUCCESS] Driver 10X nhận đơn thành công + 4 dòng [FAILED] OptimisticLockException + bảng tổng kết 'Nhận đơn thành công: 1 / OptimisticLock: 4'</t>
+  </si>
+  <si>
+    <t>Sau khi test 5-driver-1-order hoạt động đúng, nhóm muốn mở rộng kịch bản lên 10 tài xế tranh 6 đơn hàng để mô phỏng sát hơn tình huống thực tế của Food Delivery, đồng thời vẫn đảm bảo assert chính xác.</t>
+  </si>
+  <si>
+    <t>"oke sửa đi" (yêu cầu AI mở rộng kịch bản 10 tài xế - 6 đơn hàng, phân phối và assert đúng)</t>
+  </si>
+  <si>
+    <t>AI đề xuất cấu trúc với NUM_DRIVERS=10, NUM_ORDERS=6 làm hằng số class. Phân phối tài xế sang đơn theo công thức: orderId = ((driverId - 101) % numOrders) + 1. Kết quả: Driver 101→Order1, 102→Order2, ..., 106→Order6, 107→Order1, ..., 110→Order4. Order 1-4 bị 2 tài xế tranh, Order 5-6 chỉ 1 tài xế → successCount=6, exceptionCount=4. Sửa assert thành assertEquals(numOrders, successCount) và assertEquals(numDrivers-numOrders, exceptionCount). Thêm vòng assert cuối kiểm tra từng order: status=CONFIRMED, driverId!=null, version=1.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Công thức phân phối ((driverId - 101) % numOrders) + 1 của AI là deterministic — Order 5 và Order 6 chỉ có đúng 1 tài xế nên KHÔNG xảy ra tranh chấp thực sự, hai đơn này sẽ luôn CONFIRMED mà không qua OptimisticLockException. Bài toán Optimistic Locking chỉ được kiểm tra trên 4/6 đơn hàng, không phải toàn bộ.
+Contextualization: Để test có ý nghĩa demo concurrency cho GV, ít nhất mỗi đơn hàng cần ≥2 tài xế tranh chấp — tức là phải dùng NUM_DRIVERS &gt; 2×NUM_ORDERS hoặc đổi sang phân phối random.
+Creative Synthesis: Áp dụng nguyên xi phân phối deterministic của AI cho kịch bản 10-driver-6-order vì đủ để demo cơ chế Optimistic Locking (4 order vẫn có tranh chấp). Ghi chú vào comment code giải thích trade-off để tránh bị GV hỏi 'tại sao Order 5-6 không có OptimisticLockException'.
+Decision: Dùng công thức AI đề xuất, giữ NUM_DRIVERS=10, NUM_ORDERS=6, thêm comment giải thích phân phối; không đổi sang random vì kết quả assert sẽ không deterministic.</t>
+  </si>
+  <si>
+    <t>Console output bảng kết quả: successCount=6, exceptionCount=4, otherError=0 + bảng 6 đơn hàng với CONFIRMED/version=1 + comment code giải thích phân phối deterministic</t>
+  </si>
+  <si>
+    <t>Sau khi mở rộng kịch bản lên 10-driver-6-order, GV hỏi thêm về cách random số trong Java và liệu có thể dùng random để phân phối tài xế vào đơn hàng thay vì công thức modulo cố định.</t>
+  </si>
+  <si>
+    <t>"hàm random số trong jv"</t>
+  </si>
+  <si>
+    <t>AI liệt kê 4 cách: (1) Math.random() trả về double [0.0, 1.0), (2) công thức (int)(Math.random()*(max-min+1))+min để lấy int trong khoảng bất kỳ, (3) new Random() với rand.nextInt(n) trả về [0, n-1], (4) ThreadLocalRandom.current().nextInt(1, n+1) — Java 17, thread-safe hơn Random. Đề xuất dùng ThreadLocalRandom để mỗi tài xế chọn orderId ngẫu nhiên thay vì công thức modulo.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: AI đề xuất ThreadLocalRandom để thay công thức modulo — tuy nhiên với assert kiểu assertEquals(numOrders, successCount), random phân phối sẽ gây ra xác suất cao một số đơn không có tài xế nào chọn (nếu random tạo ra 10 driver cùng tranh 3 đơn), successCount có thể nhỏ hơn numOrders và test FAIL không phải do lỗi logic mà do phân phối xác suất — đây là test flaky (kết quả không ổn định giữa các lần chạy).
+Contextualization: Trong JUnit test cho cơ chế Optimistic Locking, điều quan trọng là kết quả PHẢI reproducible và deterministic để GV review được; test flaky là anti-pattern nghiêm trọng trong môi trường học thuật lẫn production.
+Creative Synthesis: Ghi nhận 4 cách random mà AI trình bày vào tài liệu học tập. Chỉ dùng ThreadLocalRandom trong setUp() để tạo dữ liệu mẫu (sinh customerId/totalPrice ngẫu nhiên), KHÔNG dùng để phân phối orderId trong vòng lặp tranh chấp.
+Decision: Giữ công thức modulo deterministic cho phân phối driver→order; bổ sung ThreadLocalRandom vào setUp() cho dữ liệu mẫu thực tế hơn (customerId random 1-2000).</t>
+  </si>
+  <si>
+    <t>Đoạn code setUp() dùng ThreadLocalRandom sinh customerId/totalPrice ngẫu nhiên + giải thích trong comment tại sao KHÔNG dùng random cho phân phối orderId trong test</t>
+  </si>
+  <si>
+    <t>Trong quá trình chạy test trên Windows, file CSV test_orders_junit4.csv bị lock bởi OS sau khi JUnit kết thúc — các lần chạy lại liên tiếp gây lỗi 'The process cannot access the file because it is being used by another process'. tearDown() dùng file.delete() nhưng vẫn thất bại do Java's GC chưa giải phóng FileInputStream.</t>
+  </si>
+  <si>
+    <t>"phát hiện lỗi" + "đây là lỗi gì" (kèm 2 screenshot lỗi file lock từ SSMS/IDE và code tearDown() dùng file.delete())</t>
+  </si>
+  <si>
+    <t>AI xác định đây là Windows File Lock — JVM giữ handle file sau khi các worker thread kết thúc nhưng GC chưa collect các Stream object. Đề xuất 2 fix: (1) thêm System.gc() trong tearDown() trước file.delete() để ép GC release handle; (2) đổi file.delete() thành file.deleteOnExit() để OS tự xóa khi JVM process thoát hoàn toàn, tránh tranh chấp lock ở mili-giây hiện tại. Giải thích: deleteOnExit() đăng ký shutdown hook với JVM, an toàn hơn delete() trực tiếp khi còn thread đang chạy.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: System.gc() KHÔNG đảm bảo GC sẽ chạy ngay lập tức — đây là 'hint' cho JVM chứ không phải lệnh bắt buộc (theo Java spec). Trên Windows với JUnit runner, System.gc() thường đủ để release handle trong practice vì thread pool đã shutdown, nhưng không phải giải pháp đảm bảo 100%.
+Contextualization: Trong môi trường CI/CD hoặc chạy test liên tục, deleteOnExit() không phải giải pháp lý tưởng vì file chỉ bị xóa khi JVM tắt hoàn toàn — nếu chạy nhiều test class liên tiếp trong cùng JVM process, file sẽ tích lũy trong thư mục.
+Creative Synthesis: Kết hợp cả hai: System.gc() trong tearDown() để release handle ngay sau test, deleteOnExit() làm safety net nếu delete() vẫn thất bại. Về dài hạn, cần đổi CsvRepository sang dùng try-with-resources đóng stream ngay sau mỗi read/write thay vì để JVM tự quản lý.
+Decision: Áp dụng System.gc() + deleteOnExit() như AI đề xuất cho bản nộp Tuần này. Ghi note kỹ thuật vào comment: đây là workaround cho Windows File Lock, không phải best practice — giải pháp đúng là CsvRepository đóng stream ngay sau dùng.</t>
+  </si>
+  <si>
+    <t>Screenshot lỗi 'The process cannot access the file' + tearDown() code sau khi fix (System.gc() + file.deleteOnExit()) + comment giải thích trade-off vs try-with-resources</t>
+  </si>
+  <si>
+    <t>008</t>
+  </si>
+  <si>
+    <t>AI viết lại method test với biến 'numOrders = 5' và vòng for in 5 đơn hàng sau assertEquals — ngụ ý setUp() đã tạo sẵn 5 đơn hàng trong file CSV.</t>
+  </si>
+  <si>
+    <t>setUp() trong code gốc chỉ tạo đúng 1 đơn hàng (order_id=1) trong file CSV test. Nếu chạy vòng for i=1..5 gọi repo.findById(i), findById(2..5) trả về null và gây NullPointerException tại assert, hoặc in ra bảng thiếu 4 dòng.</t>
+  </si>
+  <si>
+    <t>Đối chiếu code setUp() (chỉ write 1 dòng CSV) với numOrders=5 và vòng for findById(1..5) trong đề xuất của AI — nhận ra mâu thuẫn trước khi áp dụng.</t>
+  </si>
+  <si>
+    <t>Chỉ lấy phần System.out.println() từ đề xuất AI, bỏ phần thay đổi numOrders và vòng for in 5 order. Giữ nguyên cấu trúc test và setUp() ban đầu.</t>
+  </si>
+  <si>
+    <t>AI đề xuất dùng ThreadLocalRandom để mỗi tài xế chọn orderId ngẫu nhiên, khẳng định đây là cách 'giống tình huống thực tế hơn' so với công thức modulo cố định.</t>
+  </si>
+  <si>
+    <t>Dùng random cho orderId trong JUnit test tạo ra test flaky (kết quả không ổn định): random có thể khiến một số đơn không có tài xế nào tranh chấp → successCount &lt; numOrders → assertEquals(numOrders, successCount) FAIL không phải do lỗi logic mà do phân phối xác suất. Test flaky là anti-pattern nghiêm trọng trong môi trường test tự động.</t>
+  </si>
+  <si>
+    <t>Phân tích xác suất: với 10 driver random trong 6 đơn, xác suất ít nhất 1 đơn không được chọn là ~15% → test sẽ fail khoảng 1/6 lần chạy mà không có lỗi thực sự trong code.</t>
+  </si>
+  <si>
+    <t>Giữ công thức modulo deterministic cho phân phối driver→order trong vòng lặp tranh chấp; chỉ dùng ThreadLocalRandom trong setUp() để sinh dữ liệu mẫu (customerId, totalPrice).</t>
+  </si>
+  <si>
+    <t>001: console output với [SUCCESS]/[FAILED] tags; 002: bảng 6 đơn CONFIRMED/version=1; 003: phân tích xác suất ~15% fail; 004: screenshot lỗi + tearDown() code sau fix</t>
+  </si>
+  <si>
+    <t>Mỗi entry đều bác bỏ ít nhất một phần đề xuất của AI: không mở rộng numOrders (001), ghi chú trade-off deterministic/random (002-003), ghi chú workaround vs best practice (004)</t>
   </si>
 </sst>
 </file>
@@ -637,7 +724,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -749,14 +836,6 @@
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -878,7 +957,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -975,11 +1054,23 @@
     <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -988,20 +1079,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1316,14 +1401,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
     </row>
     <row r="3" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -1372,7 +1457,7 @@
         <v>55</v>
       </c>
       <c r="C10">
-        <v>28</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -1380,7 +1465,7 @@
         <v>56</v>
       </c>
       <c r="C11" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -1389,7 +1474,7 @@
       </c>
       <c r="C12" s="4">
         <f>C11/C10</f>
-        <v>0.14285714285714285</v>
+        <v>0.17777777777777778</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>58</v>
@@ -1400,7 +1485,7 @@
         <v>59</v>
       </c>
       <c r="C13" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1486,7 +1571,7 @@
         <v>66</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D21" t="s">
         <v>78</v>
@@ -1575,28 +1660,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
     </row>
     <row r="3" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
@@ -1646,7 +1731,7 @@
       <c r="G4" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="47" t="s">
+      <c r="H4" s="40" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1702,7 +1787,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="109.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="151.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="37" t="s">
         <v>18</v>
       </c>
@@ -1728,45 +1813,109 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-    </row>
-    <row r="9" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-    </row>
-    <row r="10" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
+    <row r="8" spans="1:8" ht="130.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>192</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>193</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>194</v>
+      </c>
+      <c r="G8" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="H8" s="22" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="249" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>198</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>199</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>200</v>
+      </c>
+      <c r="H9" s="25" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="205.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>202</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>203</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>204</v>
+      </c>
+      <c r="G10" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="H10" s="27" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="37" t="s">
+        <v>212</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>207</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>208</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>209</v>
+      </c>
+      <c r="G11" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="H11" s="22" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="12" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7"/>
@@ -1899,33 +2048,33 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="22" style="46" customWidth="1"/>
+    <col min="2" max="2" width="22" style="39" customWidth="1"/>
     <col min="3" max="6" width="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
     </row>
     <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
@@ -1947,101 +2096,113 @@
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="44" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="C4" s="7" t="s">
+    <row r="4" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="C4" s="48" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="D4" s="48" t="s">
         <v>96</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="E4" s="48" t="s">
         <v>97</v>
       </c>
+      <c r="F4" s="48" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="5" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="35" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" s="27" t="s">
+      <c r="A5" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="C5" s="49" t="s">
         <v>100</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="D5" s="49" t="s">
         <v>101</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="E5" s="49" t="s">
         <v>102</v>
       </c>
+      <c r="F5" s="49" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="6" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="45" t="s">
-        <v>103</v>
-      </c>
-      <c r="C6" s="31" t="s">
+      <c r="A6" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="48" t="s">
         <v>104</v>
       </c>
-      <c r="D6" s="31" t="s">
+      <c r="D6" s="48" t="s">
         <v>105</v>
       </c>
-      <c r="E6" s="31" t="s">
+      <c r="E6" s="48" t="s">
         <v>106</v>
       </c>
-      <c r="F6" s="31" t="s">
+      <c r="F6" s="48" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="99" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="35" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>109</v>
-      </c>
-      <c r="E7" s="27" t="s">
-        <v>110</v>
-      </c>
-      <c r="F7" s="27" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
+        <v>94</v>
+      </c>
+      <c r="C7" s="48" t="s">
+        <v>213</v>
+      </c>
+      <c r="D7" s="48" t="s">
+        <v>214</v>
+      </c>
+      <c r="E7" s="48" t="s">
+        <v>215</v>
+      </c>
+      <c r="F7" s="48" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="148.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="49" t="s">
+        <v>217</v>
+      </c>
+      <c r="D8" s="49" t="s">
+        <v>218</v>
+      </c>
+      <c r="E8" s="49" t="s">
+        <v>219</v>
+      </c>
+      <c r="F8" s="49" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="7"/>
+      <c r="A9" s="9"/>
       <c r="B9" s="9"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7"/>
@@ -2155,7 +2316,7 @@
       <c r="E23" s="7"/>
       <c r="F23" s="7"/>
     </row>
-    <row r="24" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="7"/>
       <c r="B24" s="9"/>
       <c r="C24" s="7"/>
@@ -2179,145 +2340,137 @@
       <c r="E26" s="7"/>
       <c r="F26" s="7"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="7"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-    </row>
-    <row r="30" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="33" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="1" t="s">
+    <row r="29" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="B33" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B34" s="9" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="10" t="s">
+      <c r="C34" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="B34" s="17" t="s">
+    </row>
+    <row r="35" spans="1:6" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B35" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="C35" s="7" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="B35" s="9" t="s">
+    <row r="36" spans="1:6" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B36" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C36" s="7" t="s">
         <v>117</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="7" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="B37" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="C37" s="7" t="s">
         <v>120</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B38" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="C38" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="C38" s="7" t="s">
+    </row>
+    <row r="39" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="B39" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="C39" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="D39" s="27" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="7" t="s">
+      <c r="E39" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="F39" s="27" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="57" x14ac:dyDescent="0.3">
+      <c r="A40" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B40" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="C40" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="D40" s="31" t="s">
         <v>125</v>
       </c>
-      <c r="B39" s="9" t="s">
+      <c r="E40" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="F40" s="31" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="57" x14ac:dyDescent="0.3">
+      <c r="A41" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="B41" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="C41" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="D41" s="27" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="29" t="s">
-        <v>24</v>
-      </c>
-      <c r="B40" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="C40" s="27" t="s">
-        <v>99</v>
-      </c>
-      <c r="D40" s="27" t="s">
+      <c r="E41" s="27" t="s">
         <v>128</v>
       </c>
-      <c r="E40" s="27" t="s">
-        <v>101</v>
-      </c>
-      <c r="F40" s="27" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="57" x14ac:dyDescent="0.3">
-      <c r="A41" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="B41" s="45" t="s">
-        <v>103</v>
-      </c>
-      <c r="C41" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="D41" s="31" t="s">
+      <c r="F41" s="27" t="s">
         <v>129</v>
-      </c>
-      <c r="E41" s="31" t="s">
-        <v>106</v>
-      </c>
-      <c r="F41" s="31" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="57" x14ac:dyDescent="0.3">
-      <c r="A42" s="29" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="C42" s="27" t="s">
-        <v>130</v>
-      </c>
-      <c r="D42" s="27" t="s">
-        <v>131</v>
-      </c>
-      <c r="E42" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="F42" s="27" t="s">
-        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -2339,222 +2492,222 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="38" t="s">
-        <v>134</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
+      <c r="A1" s="41" t="s">
+        <v>130</v>
+      </c>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="43" t="s">
-        <v>135</v>
-      </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
+        <v>131</v>
+      </c>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>139</v>
+      </c>
+      <c r="D8" s="33" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="B9" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="C9" s="32" t="s">
+        <v>139</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="12" t="s">
         <v>147</v>
       </c>
-      <c r="C8" s="32" t="s">
-        <v>143</v>
-      </c>
-      <c r="D8" s="33" t="s">
+      <c r="B10" s="13" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="C9" s="32" t="s">
-        <v>143</v>
-      </c>
-      <c r="D9" s="33" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>152</v>
-      </c>
       <c r="C10" s="32" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>153</v>
+        <v>222</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C14" s="32" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2562,13 +2715,13 @@
         <v>2</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -2576,13 +2729,13 @@
         <v>10</v>
       </c>
       <c r="B28" s="34" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C28" s="34" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D28" s="33" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -2590,13 +2743,13 @@
         <v>13</v>
       </c>
       <c r="B29" s="34" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C29" s="34" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -2604,13 +2757,13 @@
         <v>16</v>
       </c>
       <c r="B30" s="34" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C30" s="34" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D30" s="33" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -2618,13 +2771,13 @@
         <v>18</v>
       </c>
       <c r="B31" s="34" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C31" s="34" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D31" s="33" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -2632,13 +2785,13 @@
         <v>24</v>
       </c>
       <c r="B32" s="34" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C32" s="34" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D32" s="33" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -2646,13 +2799,13 @@
         <v>30</v>
       </c>
       <c r="B33" s="34" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C33" s="34" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D33" s="33" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -2660,13 +2813,13 @@
         <v>37</v>
       </c>
       <c r="B34" s="34" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C34" s="34" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D34" s="33" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>

--- a/ai_logs/Nguyên_AI_Log.xlsx
+++ b/ai_logs/Nguyên_AI_Log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\SUM26\labl\Food_delivery\ai_logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E583E022-5924-40B2-B326-1A7E1BD061D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCA8FBC3-9741-4B40-A99A-86F524E3FFB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="261">
   <si>
     <t>DETAILED AI AUDIT LOG</t>
   </si>
@@ -715,6 +715,135 @@
   </si>
   <si>
     <t>Mỗi entry đều bác bỏ ít nhất một phần đề xuất của AI: không mở rộng numOrders (001), ghi chú trade-off deterministic/random (002-003), ghi chú workaround vs best practice (004)</t>
+  </si>
+  <si>
+    <t>walkthrough.md từ Antigravity IDE + console flow: Restaurant confirm → 'Đã gán tài xế ID=X gần nhất' → Driver menu hiện đơn → accept/deny + comment code '// Euclidean approximation, acceptable for &lt;50km'</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Cơ chế 'gần nhất' của AI dựa trên tọa độ lat/lng từ CSV — nhưng DataGenerator tạo tọa độ ngẫu nhiên trong khoảng nhỏ (10.73-10.88°N, 106.60-106.75°E), tất cả driver và restaurant đều cách nhau rất gần về mặt số học. Thuật toán Haversine (hoặc Euclidean distance) sẽ cho ra 'gần nhất' nhưng sự khác biệt giữa driver thứ 1 và driver thứ 10 chỉ là vài trăm mét trong dữ liệu mô phỏng — không có ý nghĩa thực tế, chỉ là để demo cơ chế.
+Contextualization: GV sẽ hỏi 'thuật toán tìm gần nhất là gì?' — cần chuẩn bị trả lời chính xác: Euclidean distance trên tọa độ lat/lng, không phải Haversine full (quá phức tạp cho phạm vi LAB211).
+Creative Synthesis: Thuật toán Euclidean đủ dùng cho demo nhưng cần thêm comment vào code giải thích đây là approximation (sai số chấp nhận được ở khoảng cách &lt;50km). Luồng deny→reassign với excludedIds là thiết kế thông minh và phù hợp bài toán Race Condition (tránh gán trùng tài xế đã từ chối).
+Decision: Giữ nguyên toàn bộ thiết kế AI: Euclidean distance + excludedIds list + BUSY state khi gán. Thêm comment giải thích approximation. Bản này là final cho phần Driver của project.</t>
+  </si>
+  <si>
+    <t>AI đọc 10 file (MainApplication, OrderService, SimulatorView, DriverController, RestaurantController, Order, OrderStatus, OrderRepository, DriverRepository, OrderController) trước khi viết. Thay đổi: (1) Thêm hàm tìm tài xế AVAILABLE gần nhất có excludedIds để loại tài xế đã từ chối; (2) Khi Restaurant confirm đơn → tự động gán driver gần nhất, đổi driver sang BUSY; (3) Driver menu option 3: xem đơn được gán → nhấn 1=Accept (DELIVERING, tiếp tục BUSY) hoặc 2=Deny (tài xế về AVAILABLE, hệ thống tìm driver tiếp theo). Tạo walkthrough.md tóm tắt thay đổi.</t>
+  </si>
+  <si>
+    <t>"t muốn các đơn hàng phải đc tự gán cho tài xế AVAILABLE gần nhất chứ k phải tài xế chủ động nhập ID đơn hàng, tài xế có quyền accept hoặc denied đơn hàng chứ k phải nhập id để nhận đơn"</t>
+  </si>
+  <si>
+    <t>Sau khi MainApp hoàn chỉnh, nhận phản hồi mới: luồng Driver ban đầu (tài xế chủ động nhập ID đơn) không phù hợp thực tế. Cần refactor sang hệ thống tự động gán đơn: khi Restaurant confirm đơn, hệ thống tự tìm tài xế AVAILABLE gần nhất và gán; tài xế chỉ cần accept hoặc deny.</t>
+  </si>
+  <si>
+    <t>009</t>
+  </si>
+  <si>
+    <t>Console output: Restaurant X chỉ thấy ~25 đơn (thay vì 5000) + lịch sử hiển thị cả DELIVERED và CANCELLED + note 'known limitation: feedback in-memory only'</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Giải pháp lưu feedback in-memory (List&lt;String&gt; feedbacks) của AI sẽ bị mất hoàn toàn khi restart chương trình — mỗi lần khởi động lại, restaurant sẽ thấy 0 feedback mặc dù customer đã đánh giá trước đó. Điều này đặc biệt quan trọng nếu GV tắt và mở lại app giữa buổi demo.
+Contextualization: Trong phạm vi LAB211 (không có real-time server), giải pháp đúng là persist feedback ra file CSV riêng hoặc append vào orders.csv. Tuy nhiên đây sẽ thêm ~2h coding và có nguy cơ break DataGenerator compatibility.
+Creative Synthesis: Giải pháp trade-off: giữ in-memory nhưng lên kịch bản demo sao cho Customer đánh giá NGAY trong cùng session — không tắt restart app giữa chừng. Ghi chú limitation vào báo cáo như 'known limitation: feedback not persisted'.
+Decision: Giữ in-memory feedback của AI cho bản demo; ghi rõ limitation trong báo cáo; bổ sung fix isOrderForRestaurant() và hiển thị CANCELLED — đây là 2 fix quan trọng hơn và đã được AI xử lý đúng.</t>
+  </si>
+  <si>
+    <t>AI viết hàm isOrderForRestaurant() filter đơn theo restaurantId trước khi hiển thị; cập nhật lịch sử đơn hàng Restaurant hiển thị cả DELIVERED và CANCELLED; liên kết feedback Customer với màn hình Restaurant option 7 (lưu in-memory, đọc theo restaurantId); biên dịch thành công. Trả lời câu hỏi mật khẩu Admin: 'Mật khẩu để đăng nhập vào tài khoản của Admin là: admin'.</t>
+  </si>
+  <si>
+    <t>"các đơn hàng của nhà hàng chưa được link với database, restaurant có quá nhiều nhà hàng (trong data thì 5000 đơn chia cho 200 nhà hàng), các đơn bị CANCELED cũng phải được hiển thị. Đánh giá của customer chưa được hiển thị trên restaurant, hãy thêm chức năng xem đánh giá cho restaurant. cho tôi mật khẩu của ADMIN"</t>
+  </si>
+  <si>
+    <t>Sau khi tách menu, phát hiện 3 vấn đề data: (1) đơn hàng của nhà hàng chưa được filter theo restaurantId — Restaurant A thấy đơn của Restaurant B; (2) đơn CANCELED không hiển thị trong lịch sử; (3) feedback Customer chưa link với màn hình Restaurant. Cần fix trước demo.</t>
+  </si>
+  <si>
+    <t>Menu Restaurant mới: 8 option riêng biệt (list chụp từ console output) + comment code giải thích sub-menu option 4</t>
+  </si>
+  <si>
+    <t>Critical Thinking: AI tách đúng menu nhưng option 4 (Xử lý đơn hàng) vẫn gộp chung Xem PENDING + Confirm + Cancel trong 1 sub-menu — về mặt UX đây là hợp lý (3 action liên quan đến cùng 1 workflow), nhưng AI không giải thích tại sao không tách tiếp, có thể gây nhầm lẫn khi GV hỏi 'sao option này có 3 lựa chọn?'.
+Contextualization: Sub-menu gộp cho workflow Confirm/Cancel đơn là acceptable vì GV thường chấp nhận khi các action có quan hệ logic với nhau (xem đơn trước rồi mới confirm/cancel).
+Creative Synthesis: Thêm comment vào code giải thích tại sao option 4 giữ sub-menu (workflow cohesion), giúp trả lời GV nhanh trong buổi demo.
+Decision: Chấp nhận cấu trúc 8 option + sub-menu ở option 4; không tách thêm vì làm vậy sẽ tạo menu quá phẳng và nhiều bước navigate hơn khi demo.</t>
+  </si>
+  <si>
+    <t>AI đọc toàn bộ handleRestaurantMenu() (dùng lệnh Select-String -Context 0,100), tách menu Restaurant thành 8 option riêng biệt: 1-Đóng/Mở nhà hàng, 2-Thêm món mới, 3-Cập nhật giá/tồn kho, 4-Xử lý đơn hàng (Pending), 5-Theo dõi đơn đang xử lý, 6-Xem đơn đã giao (mới thêm), 7-Quản lý phản hồi (tách riêng), 8-Thanh toán &amp; Hoàn tiền (tách riêng). Customer và Driver cũng được tách tương tự. Biên dịch thành công.</t>
+  </si>
+  <si>
+    <t>"User: các tính năng chia ra riêng biệt, không gộp chung lại. Restaurant: thêm tính năng xem các đơn hàng đã giao, chức năng 5 trong restaurant đang bị gộp, hãy tách nó ra"</t>
+  </si>
+  <si>
+    <t>GV review demo lần 1 và phát hiện: (1) các tính năng bị gộp chung trong 1 menu item, (2) Restaurant thiếu tính năng xem đơn đã giao, (3) chức năng 5 của Restaurant chứa nhiều action trong 1 option. Cần tách riêng và thêm mới trước khi demo chính thức.</t>
+  </si>
+  <si>
+    <t>MainApp.java compiled + note TODO tách menu + bảng so sánh trước/sau Customer flow (xem giá ngay vs view food detail)</t>
+  </si>
+  <si>
+    <t>Critical Thinking: AI gộp chung nhiều tính năng vào 1 menu item cho cả Customer lẫn Restaurant — ví dụ 'Chức năng 5 Restaurant' chứa cả update giá, update tồn kho, và thêm món mới trong cùng 1 nhánh switch. Điều này làm menu khó navigate khi demo và GV sẽ không thấy rõ từng feature.
+Contextualization: Khi demo trực tiếp, người thuyết trình cần bấm từng option rõ ràng — menu gộp sẽ làm khán giả mất hướng và bị hỏi 'option này làm gì?'.
+Creative Synthesis: Giữ nguyên logic backend (SHA-256 auth, tồn kho, tổng tiền) của AI; yêu cầu AI refactor riêng menu structure thành từng option độc lập trong sprint tiếp theo thay vì sửa luôn bây giờ để tránh regression.
+Decision: Merge code AI, test compile pass, log TODO: tách menu Customer và Restaurant thành từng option riêng biệt trước buổi demo.</t>
+  </si>
+  <si>
+    <t>AI tạo implementation plan, mở rộng MainApp với: SHA-256 trong đăng ký/đăng nhập lấy từ DataGenerator.hashPassword(); Customer: xem giá ngay khi chọn nhà hàng, tổng tiền hiện tại checkout, hủy đơn, mô phỏng rating/feedback; Restaurant: thêm món mới độc lập (không replace toàn bộ menu), confirm/cancel đơn, update giá/tồn kho; Driver: nhận đơn CONFIRMED, giao thành công, hủy đơn trả lại, mô phỏng QR payment. File biên dịch thành công.</t>
+  </si>
+  <si>
+    <t>"dựa trên use case này, code các luồng hoạt động của từng role. Trong Customer bỏ chức năng view food item detail mà thay vào đó giá tiền sẽ đc hiển thị khi cus chọn nhà hàng và place order sẽ hiển thị giá tổng. Restaurant bỏ create new menu, nó chỉ thêm món mới chứ k thay toàn bộ menu. Sử dụng bộ dữ liệu có sẵn từ Data gene để thực hiện dự án này"</t>
+  </si>
+  <si>
+    <t>Sau khi có MainApp v1, cần tinh chỉnh UX theo use case diagram: Customer bỏ view food item detail (hiển thị giá ngay khi chọn nhà hàng và place order), Restaurant bỏ 'create new menu' (chỉ thêm món mới, không thay toàn bộ menu), tích hợp SHA-256 từ DataGenerator vào auth flow, dùng bộ dữ liệu có sẵn.</t>
+  </si>
+  <si>
+    <t>MainApp.java biên dịch thành công (Test-Path bin\com\delivery\MainApp.class = True) + note kỹ thuật Driver flow cần refactor sang auto-assign</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Luồng Driver trong bản đầu của AI để tài xế chủ động nhập ID đơn hàng để nhận — không phản ánh đúng thực tế (Grab/Baemin gán đơn tự động, tài xế chỉ accept/deny). Ngoài ra menu Driver không có tùy chọn xem địa chỉ giao hàng trước khi quyết định nhận đơn, tạo trải nghiệm không thực tế.
+Contextualization: Đây là điểm GV sẽ hỏi trong buổi demo — 'tại sao tài xế phải nhập ID thủ công?'. Cần fix trước khi submit.
+Creative Synthesis: Chấp nhận toàn bộ luồng Customer và Restaurant của AI (đúng với use case), chỉ đánh dấu luồng Driver là cần refactor trong sprint tiếp theo.
+Decision: Merge MainApp.java với luồng Customer + Restaurant hoàn chỉnh; luồng Driver giữ tạm bản AI để project có thể chạy được, sẽ refactor sang auto-assign trong phiên làm việc tiếp theo.</t>
+  </si>
+  <si>
+    <t>AI đọc 12 file (CustomerRepository, RestaurantRepository, DriverRepository, CsvRepository, OrderRepository, MenuItemRepository, Restaurant model, DataGenerator, các task log) trước khi viết. Tạo MainApp.java với: (1) Menu 4 role; (2) Customer: đăng ký/đăng nhập SHA-256, xem nhà hàng OPEN, đặt hàng nhiều món, kiểm tra tồn kho, tính tổng tiền, xem/theo dõi đơn; (3) Restaurant: đăng nhập ID, toggle OPEN/CLOSED, xem PENDING, confirm đơn, cập nhật kho; (4) Driver: đăng ký/đăng nhập, toggle AVAILABLE/OFFLINE, xem đơn CONFIRMED chưa gán, nhận đơn DELIVERING, giao xong DELIVERED; (5) Admin: password hard-code 'admin', thống kê tổng quan. Biên dịch thành công qua 3 lần sửa lỗi javac.</t>
+  </si>
+  <si>
+    <t>"Hãy viết hàm main và các hàm hỗ trợ để thực hiện các chức năng: chọn role (User/Restaurant/Driver/Admin), đăng nhập, đăng kí. User có thể xem các shop đang hoạt động, mua nhiều sản phẩm của một Restaurant, xem đơn mua, xem trạng thái đơn hàng... Restaurant có thể xem đơn hàng mới đặt và chấp nhận, cập nhật các món ăn trong nhà hàng, bật/tắt trạng thái hoạt động. Driver có thể xem đơn hàng được gán, chấp nhận và địa chỉ phải ship hàng, bật/tắt trạng thái hoạt động..."</t>
+  </si>
+  <si>
+    <t>Dự án Food Delivery đã có Model, Repository, DataGenerator nhưng chưa có MainApp — cần thiết kế luồng console cho 4 role: Customer, Restaurant, Driver, Admin. AI cần đọc toàn bộ codebase (15+ file) trước khi viết để không tạo ra code không khớp với Model/Repository hiện có.</t>
+  </si>
+  <si>
+    <t>010</t>
+  </si>
+  <si>
+    <t>011</t>
+  </si>
+  <si>
+    <t>012</t>
+  </si>
+  <si>
+    <t>013</t>
+  </si>
+  <si>
+    <t>Thêm comment vào hàm tìm tài xế: '// Euclidean approximation on lat/lng, ~2% error acceptable for simulation (&lt;50km range)'; chuẩn bị câu trả lời cho GV: đây là approximation đủ dùng cho phạm vi mô phỏng, không phải Haversine production-grade.</t>
+  </si>
+  <si>
+    <t>Phân tích khoảng giá trị tọa độ trong DataGenerator.java; đối chiếu công thức Euclidean distance trong code AI với công thức Haversine chuẩn để xác định mức độ xấp xỉ.</t>
+  </si>
+  <si>
+    <t>DataGenerator tạo tọa độ ngẫu nhiên trong khoảng lat [10.73, 10.88] và lng [106.60, 106.75] — tất cả driver và restaurant cách nhau tối đa ~20km trong dữ liệu mô phỏng. Euclidean distance trên tọa độ độ (degree) khác với khoảng cách thực tế mét — 1° lat ≈ 111km nhưng 1° lng ở vĩ độ 10° ≈ 109km, sai số khoảng 2% (chấp nhận được), nhưng không nên gọi đây là thuật toán chính xác địa lý khi báo cáo.</t>
+  </si>
+  <si>
+    <t>Thuật toán 'tìm tài xế gần nhất' mà AI cài đặt (dựa trên Euclidean distance của tọa độ lat/lng) phản ánh đúng thực tế địa lý và đủ để nói 'hệ thống tìm tài xế gần nhất' trong báo cáo mà không cần giải thích thêm.</t>
+  </si>
+  <si>
+    <t>Giữ in-memory cho bản demo nhưng lên kịch bản demo không restart app; ghi 'known limitation: feedback not persisted across sessions' vào báo cáo; đánh dấu là technical debt cần fix nếu có thêm thời gian.</t>
+  </si>
+  <si>
+    <t>Đọc code implementation: feedbacks được khai báo là 'static List&lt;String&gt;', không có lệnh ghi ra file CSV hay bất kỳ persistence nào — confirmed là in-memory only.</t>
+  </si>
+  <si>
+    <t>In-memory List bị xóa sạch mỗi lần restart JVM. Nếu GV tắt và mở lại app trong buổi demo, tất cả feedback biến mất — Restaurant thấy 0 đánh giá dù Customer vừa đánh giá xong trong session trước. Feedback không thực sự 'linked với database'.</t>
+  </si>
+  <si>
+    <t>AI lưu feedback của Customer vào List&lt;String&gt; in-memory và khẳng định Restaurant có thể 'đọc được những phản hồi chính xác này từ khách' qua chức năng Quản lý phản hồi — ngụ ý feedback tồn tại lâu dài như dữ liệu thật.</t>
   </si>
 </sst>
 </file>
@@ -957,7 +1086,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1063,30 +1192,36 @@
     <xf numFmtId="0" fontId="20" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1401,14 +1536,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
     </row>
     <row r="3" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -1457,7 +1592,7 @@
         <v>55</v>
       </c>
       <c r="C10">
-        <v>45</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -1465,7 +1600,7 @@
         <v>56</v>
       </c>
       <c r="C11" s="3">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -1474,7 +1609,7 @@
       </c>
       <c r="C12" s="4">
         <f>C11/C10</f>
-        <v>0.17777777777777778</v>
+        <v>0.19402985074626866</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>58</v>
@@ -1485,7 +1620,7 @@
         <v>59</v>
       </c>
       <c r="C13" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1598,7 +1733,7 @@
         <v>12</v>
       </c>
       <c r="B24" s="8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C24" s="9" t="s">
         <v>84</v>
@@ -1609,7 +1744,7 @@
         <v>31</v>
       </c>
       <c r="B25" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C25" s="9" t="s">
         <v>84</v>
@@ -1620,7 +1755,7 @@
         <v>38</v>
       </c>
       <c r="B26" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C26" s="9" t="s">
         <v>84</v>
@@ -1631,7 +1766,7 @@
         <v>15</v>
       </c>
       <c r="B27" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C27" s="9" t="s">
         <v>84</v>
@@ -1660,28 +1795,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
     </row>
     <row r="3" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
@@ -1917,55 +2052,135 @@
         <v>211</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-    </row>
-    <row r="13" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-    </row>
-    <row r="14" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-    </row>
-    <row r="15" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-    </row>
-    <row r="16" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
+    <row r="12" spans="1:8" ht="200.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="37" t="s">
+        <v>228</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>248</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>247</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>246</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>245</v>
+      </c>
+      <c r="H12" s="22" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="202.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="37" t="s">
+        <v>249</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>243</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>242</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>241</v>
+      </c>
+      <c r="G13" s="25" t="s">
+        <v>240</v>
+      </c>
+      <c r="H13" s="25" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="200.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="37" t="s">
+        <v>250</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="27" t="s">
+        <v>238</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>237</v>
+      </c>
+      <c r="F14" s="27" t="s">
+        <v>236</v>
+      </c>
+      <c r="G14" s="27" t="s">
+        <v>235</v>
+      </c>
+      <c r="H14" s="27" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="196.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="B15" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>232</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="G15" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="H15" s="22" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="222.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="37" t="s">
+        <v>252</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>226</v>
+      </c>
+      <c r="F16" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="G16" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="H16" s="25" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="17" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7"/>
@@ -2057,7 +2272,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="48" t="s">
         <v>85</v>
       </c>
       <c r="B1" s="47"/>
@@ -2067,7 +2282,7 @@
       <c r="F1" s="47"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="46" t="s">
         <v>86</v>
       </c>
       <c r="B2" s="47"/>
@@ -2103,16 +2318,16 @@
       <c r="B4" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="C4" s="48" t="s">
+      <c r="C4" s="41" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="48" t="s">
+      <c r="D4" s="41" t="s">
         <v>96</v>
       </c>
-      <c r="E4" s="48" t="s">
+      <c r="E4" s="41" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="48" t="s">
+      <c r="F4" s="41" t="s">
         <v>98</v>
       </c>
     </row>
@@ -2123,16 +2338,16 @@
       <c r="B5" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="C5" s="49" t="s">
+      <c r="C5" s="42" t="s">
         <v>100</v>
       </c>
-      <c r="D5" s="49" t="s">
+      <c r="D5" s="42" t="s">
         <v>101</v>
       </c>
-      <c r="E5" s="49" t="s">
+      <c r="E5" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="F5" s="49" t="s">
+      <c r="F5" s="42" t="s">
         <v>103</v>
       </c>
     </row>
@@ -2143,16 +2358,16 @@
       <c r="B6" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="C6" s="48" t="s">
+      <c r="C6" s="41" t="s">
         <v>104</v>
       </c>
-      <c r="D6" s="48" t="s">
+      <c r="D6" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="E6" s="48" t="s">
+      <c r="E6" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="F6" s="48" t="s">
+      <c r="F6" s="41" t="s">
         <v>107</v>
       </c>
     </row>
@@ -2163,16 +2378,16 @@
       <c r="B7" s="26" t="s">
         <v>94</v>
       </c>
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="41" t="s">
         <v>213</v>
       </c>
-      <c r="D7" s="48" t="s">
+      <c r="D7" s="41" t="s">
         <v>214</v>
       </c>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="41" t="s">
         <v>215</v>
       </c>
-      <c r="F7" s="48" t="s">
+      <c r="F7" s="41" t="s">
         <v>216</v>
       </c>
     </row>
@@ -2183,34 +2398,58 @@
       <c r="B8" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="C8" s="49" t="s">
+      <c r="C8" s="42" t="s">
         <v>217</v>
       </c>
-      <c r="D8" s="49" t="s">
+      <c r="D8" s="42" t="s">
         <v>218</v>
       </c>
-      <c r="E8" s="49" t="s">
+      <c r="E8" s="42" t="s">
         <v>219</v>
       </c>
-      <c r="F8" s="49" t="s">
+      <c r="F8" s="42" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-    </row>
-    <row r="10" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
+    <row r="9" spans="1:6" ht="127.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="35" t="s">
+        <v>251</v>
+      </c>
+      <c r="B9" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>260</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>259</v>
+      </c>
+      <c r="E9" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="F9" s="27" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="136.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="36" t="s">
+        <v>252</v>
+      </c>
+      <c r="B10" s="50" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>256</v>
+      </c>
+      <c r="D10" s="31" t="s">
+        <v>255</v>
+      </c>
+      <c r="E10" s="31" t="s">
+        <v>254</v>
+      </c>
+      <c r="F10" s="31" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="11" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7"/>
@@ -2492,20 +2731,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="45" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="49" t="s">
         <v>131</v>
       </c>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">

--- a/ai_logs/Nguyên_AI_Log.xlsx
+++ b/ai_logs/Nguyên_AI_Log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\SUM26\labl\Food_delivery\ai_logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCA8FBC3-9741-4B40-A99A-86F524E3FFB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{203A5EE5-78E2-492A-AC69-3FEE70DDF38B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="299">
   <si>
     <t>DETAILED AI AUDIT LOG</t>
   </si>
@@ -844,6 +844,135 @@
   </si>
   <si>
     <t>AI lưu feedback của Customer vào List&lt;String&gt; in-memory và khẳng định Restaurant có thể 'đọc được những phản hồi chính xác này từ khách' qua chức năng Quản lý phản hồi — ngụ ý feedback tồn tại lâu dài như dữ liệu thật.</t>
+  </si>
+  <si>
+    <t>LockMechanism.java đã được viết sẵn với 4 enum: NO_LOCK, SYNCHRONIZED, FILE_LOCK, OPTIMISTIC. Cần hiểu rõ từng cơ chế trước khi viết báo cáo phân tích và chuẩn bị trả lời GV về lý do chọn Optimistic Locking làm cơ chế chính cho Food Delivery.</t>
+  </si>
+  <si>
+    <t>AI đọc file và giải thích 4 cơ chế: (1) NO_LOCK — không bảo vệ, nhanh nhất, dễ Race Condition khi 2 tài xế nhận cùng 1 đơn; (2) SYNCHRONIZED — Java keyword/ReentrantLock, chỉ hiệu quả trên 1 JVM, không dùng được cho Distributed System; (3) FILE_LOCK — dùng java.nio.channels.FileLock của OS, hiệu quả giữa các process trên cùng 1 máy nhưng chậm do I/O; (4) OPTIMISTIC — đọc version khi lấy data, kiểm tra version trước khi ghi, ném lỗi nếu version đã thay đổi (người khác đã cập nhật trước). Kết luận: Optimistic phù hợp nhất cho hệ thống đọc nhiều hơn ghi.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: AI giải thích SYNCHRONIZED 'không hiệu quả cho Distributed System' — đúng về lý thuyết, nhưng project này chạy trên 1 JVM duy nhất (single process, multi-thread). Trong phạm vi LAB211, SYNCHRONIZED vẫn ngăn được Race Condition hoàn toàn; hạn chế Distributed chỉ liên quan khi triển khai production thực tế, không phải bối cảnh đề bài.
+Contextualization: GV có thể hỏi 'Tại sao không dùng SYNCHRONIZED thay vì OPTIMISTIC?' — cần câu trả lời cân bằng: SYNCHRONIZED đúng cho single JVM, OPTIMISTIC đúng hơn khi muốn mô phỏng hành vi database thực tế (version column).
+Creative Synthesis: Bổ sung vào bảng so sánh 4 cơ chế trong báo cáo thêm cột 'Phạm vi áp dụng' (Single JVM / Single Machine / Distributed) để GV thấy nhóm hiểu context, không chỉ học vẹt lý thuyết.
+Decision: Dùng toàn bộ giải thích AI làm nội dung báo cáo; bổ sung thêm cột 'Phạm vi' và câu chú thích 'Trong LAB211, project chạy single JVM nên cả SYNCHRONIZED và OPTIMISTIC đều ngăn được Race Condition — OPTIMISTIC được chọn vì mô phỏng sát hành vi database thực tế hơn'.</t>
+  </si>
+  <si>
+    <t>Bảng so sánh 4 cơ chế trong báo cáo (5 cột: Tên / Phương thức / Phạm vi / Ưu điểm / Nhược điểm) + câu chú thích về single JVM context</t>
+  </si>
+  <si>
+    <t>Sau khi chạy Simulator, console in ra bảng kết quả với các con số Success/Failed/Throughput. Cần chứng minh với GV rằng các con số này không phải 'bịa ra' mà có thể verify độc lập bằng file CSV — đây là yêu cầu thực nghiệm (empirical proof) của đề bài.</t>
+  </si>
+  <si>
+    <t>AI đọc 3 file (MainApplication, SimulatorController, SimulatorView) và đề xuất 4 cách verify: (1) Tổng Success + Failed = TOTAL_CUSTOMERS=100 luôn đúng; (2) Mở menu_items.csv kiểm tra stock âm sau NO_LOCK (Oversell proof); (3) Mở orders.csv tìm driver_id xuất hiện ≥2 lần với status CONFIRMED (Overload proof); (4) Console đọc lại trực tiếp từ simulation_runs.csv chứ không phải biến RAM — mở CSV đối chiếu từng dòng.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Cách verify (4) của AI mô tả đúng nhưng cần làm rõ một điểm quan trọng: printLockComparisonTableFromFile() đọc lại từ file là đúng — nhưng nếu file CSV bị ghi sai (bug trong saveSimulationResult()), console sẽ vẫn hiển thị số sai mà verify bằng cách so sánh console với CSV cũng không phát hiện được. Verify thực sự cần đếm thủ công trong orders.csv và menu_items.csv.
+Contextualization: GV thường yêu cầu 'mở file CSV lên cho tôi xem' trong buổi demo — cần chuẩn bị sẵn 3 file CSV sau mỗi kịch bản chạy, không để lẫn giữa các lần chạy (NO_LOCK vs SYNCHRONIZED output khác nhau).
+Creative Synthesis: Xây dựng quy trình verify 3 bước cho buổi demo: Bước 1 — chạy NO_LOCK và lưu screenshot console; Bước 2 — mở menu_items.csv đếm số dòng có stockQty &lt; 0; Bước 3 — mở orders.csv dùng Excel filter driver_id và đếm CONFIRMED trùng. Ba bước này independent nhau và không phụ thuộc vào console.
+Decision: Chuẩn bị 'Verify Checklist' 3 bước cho buổi demo; chụp screenshot CSV làm evidence trong báo cáo; không chỉ dùng console screenshot.</t>
+  </si>
+  <si>
+    <t>Verify checklist 3 bước + screenshot menu_items.csv (stockQty âm sau NO_LOCK) + screenshot orders.csv (driver_id trùng CONFIRMED) + so sánh với console output</t>
+  </si>
+  <si>
+    <t>Cần tìm đúng file source code chứa logic của từng phần Simulator để phân công thành viên báo cáo và để bản thân hiểu rõ flow code trước khi GV hỏi chi tiết implementation. AI đọc LockMechanism.java nhưng cần tìm file thực thi logic.</t>
+  </si>
+  <si>
+    <t>AI grep codebase, đọc drivers.csv để hiểu data structure, chỉ ra 4 file chính: (1) SimulatorController.java — runSimulation() tạo 100 CustomerThread + 20 DispatchThread, vòng lặp 4 loại Lock, detectOversellItems(), detectDriverOverload(); (2) MenuItemRepository.java — validateAndDeductStockAtomically() là 'trái tim' xử lý đụng độ kho hàng với 3 nhánh synchronized/FileLock/version check; (3) ReportView.java — saveSimulationResult() ghi CSV, printLockComparisonTableFromFile() đọc và vẽ bảng console; (4) data/ folder — menu_items.csv, orders.csv, simulation_runs.csv.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: AI chỉ ra 4 file nhưng không đề cập đến CustomerThread.java và DispatchThread.java — đây là 2 file quan trọng nhất để hiểu RACE CONDITION xảy ra ở đâu (CustomerThread gọi validateAndDeductStockAtomically, DispatchThread gọi hàm gán tài xế). Nếu không đọc 2 file này, không thể giải thích được tại sao NO_LOCK gây lỗi ở cả 2 loại: Oversell (kho âm) và Overload (tài xế trùng).
+Contextualization: GV thường hỏi 'Race Condition xảy ra cụ thể ở đoạn code nào?' — câu trả lời phải chỉ được đúng method trong CustomerThread/DispatchThread, không chỉ nói chung chung.
+Creative Synthesis: Tự đọc thêm CustomerThread.java và DispatchThread.java để bổ sung vào sơ đồ luồng (flow diagram): Thread → gọi Repository method → Lock check → read CSV → check condition → write CSV → release Lock.
+Decision: Vẽ flow diagram đầy đủ 6 bước cho mỗi cơ chế Lock; phân công mỗi thành viên giải thích 1-2 cơ chế với flow diagram tương ứng trong buổi báo cáo.</t>
+  </si>
+  <si>
+    <t>Flow diagram 6 bước (Thread → Repository → Lock → Read → Check → Write) cho 4 cơ chế Lock + danh sách 6 file chính (thêm CustomerThread và DispatchThread)</t>
+  </si>
+  <si>
+    <t>Sau khi chạy Simulator với SYNCHRONIZED và FILE_LOCK, kết quả console luôn hiện Success = 50, Failed = 50. Nhóm không chắc đây là hành vi đúng hay Simulator đang bị bug — cần xác nhận trước khi báo cáo.</t>
+  </si>
+  <si>
+    <t>AI đọc MenuItemRepository.java và giải thích: đây là hành vi đúng, không phải bug. SYNCHRONIZED và FILE_LOCK là Pessimistic Locking — ép 100 luồng xếp hàng tuần tự. 50 người đầu lấy được lock thấy stock &gt; 0 → mua thành công. Người thứ 51 lấy lock thấy stock = 0 → từ chối (Failed). Kết quả: Success=50 = stock ban đầu, Failed=50 = 100-50. Đề xuất test: đổi TOTAL_CUSTOMERS=120 sẽ ra Success=50, Failed=70 (không còn bằng nhau) để chứng minh logic đúng.</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Giải thích của AI hoàn toàn đúng và đầy đủ về mặt lý thuyết. Tuy nhiên có một điểm tinh tế cần bổ sung cho báo cáo: với OPTIMISTIC, kết quả cũng phải là Success=50, Failed=50 nếu cơ chế hoạt động đúng — nhưng nếu OPTIMISTIC bị implement sai (ví dụ version check không atomic), Success có thể &gt; 50 (tức vẫn còn Oversell dù dùng Optimistic). Việc OPTIMISTIC cũng cho Success=50 là bằng chứng cơ chế hoạt động đúng, không phải trùng hợp.
+Contextualization: GV có thể hỏi 'Thế NO_LOCK cho Success bao nhiêu?' — câu trả lời đúng là Success &gt; 50 (thường 70-100 tùy race condition) và stockQty trong CSV bị âm. Đây mới là điểm phân biệt NO_LOCK với 3 cơ chế còn lại.
+Creative Synthesis: Áp dụng test AI đề xuất: chạy TOTAL_CUSTOMERS=120 để verify; ghi rõ trong báo cáo 'Success=50 với mọi Locking mechanism ≠ bug; nó chứng minh cả 3 cơ chế (SYNCHRONIZED/FILE_LOCK/OPTIMISTIC) đều bảo vệ đúng stock limit'.
+Decision: Chạy test TOTAL_CUSTOMERS=120 để có thêm bằng chứng; bổ sung vào báo cáo bảng kết quả với 2 kịch bản (100 và 120 customers) để chứng minh tính nhất quán của kết quả.</t>
+  </si>
+  <si>
+    <t>Console screenshot TOTAL_CUSTOMERS=100 (Success=50, Failed=50) + TOTAL_CUSTOMERS=120 (Success=50, Failed=70) cho SYNCHRONIZED và FILE_LOCK + ghi chú 'Success=50 là stock limit, không phải bug'</t>
+  </si>
+  <si>
+    <t>Bảng console in cột 'THPUT(d/s)' nhưng nhóm không rõ công thức tính throughput và cách đọc con số này để so sánh hiệu năng giữa 4 cơ chế Lock trong báo cáo. Đây là chỉ số định lượng quan trọng để trả lời câu hỏi nghiên cứu (RQ) về hiệu năng.</t>
+  </si>
+  <si>
+    <t>AI đọc SimulationRun.java, tìm đúng dòng code công thức: throughput = durationMs &gt; 0 ? (totalSuccess * 1000.0 / durationMs) : 0. Giải thích: totalSuccess (đơn thành công) × 1000 ÷ durationMs (ms) = đơn/giây. Ví dụ: 50 success ÷ 500ms × 1000 = 100 đơn/giây. Dự đoán thứ tự throughput: NO_LOCK cao nhất (không chờ), OPTIMISTIC nhì, FILE_LOCK thấp nhất (I/O latency).</t>
+  </si>
+  <si>
+    <t>Critical Thinking: Dự đoán thứ tự throughput của AI (NO_LOCK &gt; OPTIMISTIC &gt; SYNCHRONIZED &gt; FILE_LOCK) là đúng về lý thuyết, nhưng trong thực tế benchmark với 100 threads trên máy cá nhân: (a) SYNCHRONIZED và OPTIMISTIC có thể cho throughput gần tương đương vì cả hai đều phải đọc/ghi file CSV tuần tự — bottleneck thực sự là I/O disk, không phải lock overhead; (b) FILE_LOCK chậm nhất vì gọi OS-level file lock, nhưng mức chênh lệch phụ thuộc vào SSD vs HDD.
+Contextualization: GV sẽ hỏi 'Tại sao OPTIMISTIC không nhanh hơn SYNCHRONIZED nhiều như lý thuyết?' — câu trả lời: trong project này cả hai đều phải gọi readAll() và saveAll() trên file CSV, I/O là bottleneck chung, lock overhead nhỏ hơn I/O latency nên throughput không chênh nhiều.
+Creative Synthesis: Ghi rõ trong báo cáo 2 tầng: (1) Throughput lý thuyết (theo lock mechanism), (2) Throughput thực tế (bị giới hạn bởi I/O bottleneck của CSV-based storage). Thêm ghi chú: 'Với database thực (MySQL/PostgreSQL), khoảng cách OPTIMISTIC vs SYNCHRONIZED sẽ rõ hơn nhiều'.
+Decision: Dùng công thức AI cung cấp làm nội dung giải thích trong báo cáo; bổ sung phần nhận xét về I/O bottleneck và so sánh lý thuyết vs thực nghiệm để thể hiện nhóm hiểu giới hạn của mô hình CSV.</t>
+  </si>
+  <si>
+    <t>Dòng code công thức throughput trong SimulationRun.java (dòng 46/62) + bảng console 4 cơ chế Lock với cột THPUT(d/s) + nhận xét về I/O bottleneck trong báo cáo</t>
+  </si>
+  <si>
+    <t>"giải thích phần 4 cơ chế lock" (kèm LockMechanism.java)</t>
+  </si>
+  <si>
+    <t>"làm sao để chứng minh con số hiển thị trên console là đúng?"</t>
+  </si>
+  <si>
+    <t>"code của phần này ở đâu"</t>
+  </si>
+  <si>
+    <t>"tại sao synchronized và file lock luôn có success = failed"</t>
+  </si>
+  <si>
+    <t>"through put tính sao"</t>
+  </si>
+  <si>
+    <t>014</t>
+  </si>
+  <si>
+    <t>015</t>
+  </si>
+  <si>
+    <t>016</t>
+  </si>
+  <si>
+    <t>017</t>
+  </si>
+  <si>
+    <t>018</t>
+  </si>
+  <si>
+    <t>AI khẳng định SYNCHRONIZED 'không hiệu quả' và 'không còn tác dụng' cho hệ thống Food Delivery vì giới hạn Single JVM — ngụ ý OPTIMISTIC là lựa chọn duy nhất đúng cho project này.</t>
+  </si>
+  <si>
+    <t>Project LAB211 chạy hoàn toàn trên 1 JVM (single process, multi-thread). Trong phạm vi này, SYNCHRONIZED ngăn Race Condition 100% và cho kết quả Success=50 giống hệt OPTIMISTIC. Hạn chế 'Distributed System' của SYNCHRONIZED chỉ liên quan khi triển khai production thực tế trên nhiều server — không áp dụng cho ngữ cảnh LAB211.</t>
+  </si>
+  <si>
+    <t>Phân tích kết quả Simulator: SYNCHRONIZED cho Success=50 giống OPTIMISTIC, chứng minh cả hai đều hoạt động đúng trong phạm vi single JVM. Đối chiếu với lý thuyết concurrency: synchronized keyword đủ để bảo vệ shared resource trong multi-thread single process.</t>
+  </si>
+  <si>
+    <t>Bổ sung cột 'Phạm vi áp dụng' vào bảng so sánh 4 cơ chế; thêm câu chú thích: 'Trong LAB211 (single JVM), cả SYNCHRONIZED và OPTIMISTIC đều ngăn được Race Condition — OPTIMISTIC được chọn vì mô phỏng sát hành vi database version column hơn, không phải vì SYNCHRONIZED sai'.</t>
+  </si>
+  <si>
+    <t>AI dự đoán thứ tự throughput NO_LOCK &gt; OPTIMISTIC &gt; SYNCHRONIZED &gt; FILE_LOCK như một quy luật chắc chắn, ngụ ý OPTIMISTIC sẽ nhanh hơn SYNCHRONIZED rõ rệt trong kết quả benchmark của project.</t>
+  </si>
+  <si>
+    <t>Trong project dùng CSV file làm storage, bottleneck thực sự là I/O disk (readAll() và saveAll() gọi cho mọi cơ chế Lock). Lock overhead (synchronized vs version check) nhỏ hơn nhiều so với I/O latency nên OPTIMISTIC và SYNCHRONIZED thường cho throughput gần tương đương trong benchmark thực tế. Khoảng cách lý thuyết chỉ rõ khi dùng in-memory storage hoặc database thực.</t>
+  </si>
+  <si>
+    <t>Chạy Simulator và quan sát cột THPUT(d/s): SYNCHRONIZED và OPTIMISTIC cho throughput chênh lệch nhỏ hơn dự đoán của AI. Phân tích nguồn gốc: cả hai đều gọi readAll()/saveAll() — I/O là common bottleneck.</t>
+  </si>
+  <si>
+    <t>Bổ sung vào báo cáo phần 'Nhận xét thực nghiệm': throughput bị giới hạn bởi I/O bottleneck của CSV storage; thêm ghi chú 'Với database thực (MySQL), khoảng cách OPTIMISTIC vs SYNCHRONIZED sẽ rõ hơn nhiều do in-memory index'; phân biệt rõ throughput lý thuyết vs thực nghiệm trong bảng so sánh.</t>
   </si>
 </sst>
 </file>
@@ -853,7 +982,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -894,19 +1023,6 @@
       <i/>
       <sz val="10"/>
       <color rgb="FF666666"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -952,11 +1068,6 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -971,8 +1082,74 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF2E75B6"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1032,6 +1209,12 @@
         <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -1086,7 +1269,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1111,117 +1294,132 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1536,14 +1734,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
     </row>
     <row r="3" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -1795,28 +1993,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="43" t="s">
+      <c r="A2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
     </row>
     <row r="3" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
@@ -1845,7 +2043,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="109.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="32" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="20" t="s">
@@ -1866,12 +2064,12 @@
       <c r="G4" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="40" t="s">
+      <c r="H4" s="33" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="109.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="32" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="23" t="s">
@@ -1897,7 +2095,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="109.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="32" t="s">
         <v>16</v>
       </c>
       <c r="B6" s="23" t="s">
@@ -1923,7 +2121,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="151.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="32" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="28" t="s">
@@ -1949,7 +2147,7 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="130.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="32" t="s">
         <v>24</v>
       </c>
       <c r="B8" s="23" t="s">
@@ -1975,7 +2173,7 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="249" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="32" t="s">
         <v>30</v>
       </c>
       <c r="B9" s="20" t="s">
@@ -2001,7 +2199,7 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="205.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="37" t="s">
+      <c r="A10" s="32" t="s">
         <v>37</v>
       </c>
       <c r="B10" s="28" t="s">
@@ -2027,7 +2225,7 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="230.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="37" t="s">
+      <c r="A11" s="32" t="s">
         <v>212</v>
       </c>
       <c r="B11" s="23" t="s">
@@ -2053,7 +2251,7 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="200.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="32" t="s">
         <v>228</v>
       </c>
       <c r="B12" s="20" t="s">
@@ -2079,7 +2277,7 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="202.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="37" t="s">
+      <c r="A13" s="32" t="s">
         <v>249</v>
       </c>
       <c r="B13" s="20" t="s">
@@ -2105,7 +2303,7 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="200.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="37" t="s">
+      <c r="A14" s="32" t="s">
         <v>250</v>
       </c>
       <c r="B14" s="23" t="s">
@@ -2131,7 +2329,7 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="196.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="37" t="s">
+      <c r="A15" s="32" t="s">
         <v>251</v>
       </c>
       <c r="B15" s="28" t="s">
@@ -2157,7 +2355,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="222.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="37" t="s">
+      <c r="A16" s="32" t="s">
         <v>252</v>
       </c>
       <c r="B16" s="20" t="s">
@@ -2182,55 +2380,135 @@
         <v>223</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-    </row>
-    <row r="18" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-    </row>
-    <row r="19" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-    </row>
-    <row r="20" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-    </row>
-    <row r="21" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
+    <row r="17" spans="1:8" ht="208.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="32" t="s">
+        <v>286</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>261</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>262</v>
+      </c>
+      <c r="G17" s="22" t="s">
+        <v>263</v>
+      </c>
+      <c r="H17" s="22" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="187.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="32" t="s">
+        <v>287</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>265</v>
+      </c>
+      <c r="E18" s="25" t="s">
+        <v>282</v>
+      </c>
+      <c r="F18" s="25" t="s">
+        <v>266</v>
+      </c>
+      <c r="G18" s="25" t="s">
+        <v>267</v>
+      </c>
+      <c r="H18" s="25" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="175.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="32" t="s">
+        <v>288</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>269</v>
+      </c>
+      <c r="E19" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="F19" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="G19" s="27" t="s">
+        <v>271</v>
+      </c>
+      <c r="H19" s="27" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="217.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="32" t="s">
+        <v>289</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>273</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>284</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>274</v>
+      </c>
+      <c r="G20" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="H20" s="22" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="213.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="32" t="s">
+        <v>290</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>277</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>285</v>
+      </c>
+      <c r="F21" s="25" t="s">
+        <v>278</v>
+      </c>
+      <c r="G21" s="25" t="s">
+        <v>279</v>
+      </c>
+      <c r="H21" s="25" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="22" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="7"/>
@@ -2264,451 +2542,476 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F41"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="22" style="39" customWidth="1"/>
-    <col min="3" max="6" width="30" customWidth="1"/>
+    <col min="1" max="1" width="12" style="43" customWidth="1"/>
+    <col min="2" max="2" width="22" style="43" customWidth="1"/>
+    <col min="3" max="6" width="30" style="43" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="43"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
     </row>
     <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="50" t="s">
         <v>87</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="50" t="s">
         <v>91</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="50" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="C4" s="41" t="s">
+      <c r="C4" s="39" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="41" t="s">
+      <c r="D4" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="E4" s="41" t="s">
+      <c r="E4" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="41" t="s">
+      <c r="F4" s="39" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="40" t="s">
         <v>99</v>
       </c>
-      <c r="C5" s="42" t="s">
+      <c r="C5" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="D5" s="42" t="s">
+      <c r="D5" s="41" t="s">
         <v>101</v>
       </c>
-      <c r="E5" s="42" t="s">
+      <c r="E5" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="F5" s="42" t="s">
+      <c r="F5" s="41" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="35" t="s">
+      <c r="A6" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="C6" s="41" t="s">
+      <c r="C6" s="39" t="s">
         <v>104</v>
       </c>
-      <c r="D6" s="41" t="s">
+      <c r="D6" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="E6" s="41" t="s">
+      <c r="E6" s="39" t="s">
         <v>106</v>
       </c>
-      <c r="F6" s="41" t="s">
+      <c r="F6" s="39" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="C7" s="39" t="s">
         <v>213</v>
       </c>
-      <c r="D7" s="41" t="s">
+      <c r="D7" s="39" t="s">
         <v>214</v>
       </c>
-      <c r="E7" s="41" t="s">
+      <c r="E7" s="39" t="s">
         <v>215</v>
       </c>
-      <c r="F7" s="41" t="s">
+      <c r="F7" s="39" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="148.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="52" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="40" t="s">
         <v>99</v>
       </c>
-      <c r="C8" s="42" t="s">
+      <c r="C8" s="41" t="s">
         <v>217</v>
       </c>
-      <c r="D8" s="42" t="s">
+      <c r="D8" s="41" t="s">
         <v>218</v>
       </c>
-      <c r="E8" s="42" t="s">
+      <c r="E8" s="41" t="s">
         <v>219</v>
       </c>
-      <c r="F8" s="42" t="s">
+      <c r="F8" s="41" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="127.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="35" t="s">
+      <c r="A9" s="51" t="s">
         <v>251</v>
       </c>
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="39" t="s">
         <v>260</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D9" s="39" t="s">
         <v>259</v>
       </c>
-      <c r="E9" s="27" t="s">
+      <c r="E9" s="39" t="s">
         <v>258</v>
       </c>
-      <c r="F9" s="27" t="s">
+      <c r="F9" s="39" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="136.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="36" t="s">
+      <c r="A10" s="52" t="s">
         <v>252</v>
       </c>
-      <c r="B10" s="50" t="s">
+      <c r="B10" s="40" t="s">
         <v>99</v>
       </c>
-      <c r="C10" s="31" t="s">
+      <c r="C10" s="41" t="s">
         <v>256</v>
       </c>
-      <c r="D10" s="31" t="s">
+      <c r="D10" s="41" t="s">
         <v>255</v>
       </c>
-      <c r="E10" s="31" t="s">
+      <c r="E10" s="41" t="s">
         <v>254</v>
       </c>
-      <c r="F10" s="31" t="s">
+      <c r="F10" s="41" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="7"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-    </row>
-    <row r="12" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
+    <row r="11" spans="1:6" ht="133.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="55" t="s">
+        <v>286</v>
+      </c>
+      <c r="B11" s="56" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" s="53" t="s">
+        <v>291</v>
+      </c>
+      <c r="D11" s="53" t="s">
+        <v>292</v>
+      </c>
+      <c r="E11" s="53" t="s">
+        <v>293</v>
+      </c>
+      <c r="F11" s="53" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="141" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="55" t="s">
+        <v>290</v>
+      </c>
+      <c r="B12" s="56" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" s="53" t="s">
+        <v>295</v>
+      </c>
+      <c r="D12" s="53" t="s">
+        <v>296</v>
+      </c>
+      <c r="E12" s="53" t="s">
+        <v>297</v>
+      </c>
+      <c r="F12" s="53" t="s">
+        <v>298</v>
+      </c>
     </row>
     <row r="13" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
+      <c r="A13" s="42"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
     </row>
     <row r="14" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="7"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
+      <c r="A14" s="42"/>
+      <c r="B14" s="42"/>
+      <c r="C14" s="42"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
     </row>
     <row r="15" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="7"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
+      <c r="A15" s="42"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
     </row>
     <row r="16" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="7"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
+      <c r="A16" s="42"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="42"/>
     </row>
     <row r="17" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="7"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
+      <c r="A17" s="42"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="42"/>
+      <c r="D17" s="42"/>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
     </row>
     <row r="18" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="7"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
+      <c r="A18" s="42"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
     </row>
     <row r="19" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="7"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
+      <c r="A19" s="42"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="42"/>
+      <c r="D19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
     </row>
     <row r="20" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="7"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
+      <c r="A20" s="42"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
+      <c r="E20" s="42"/>
+      <c r="F20" s="42"/>
     </row>
     <row r="21" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="7"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
+      <c r="A21" s="42"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="42"/>
+      <c r="E21" s="42"/>
+      <c r="F21" s="42"/>
     </row>
     <row r="22" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="7"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
+      <c r="A22" s="42"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
     </row>
     <row r="23" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="7"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
+      <c r="A23" s="42"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="42"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="7"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
+      <c r="A24" s="42"/>
+      <c r="B24" s="42"/>
+      <c r="C24" s="42"/>
+      <c r="D24" s="42"/>
+      <c r="E24" s="42"/>
+      <c r="F24" s="42"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="7"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
+      <c r="A25" s="42"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="7"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
+      <c r="A26" s="42"/>
+      <c r="B26" s="42"/>
+      <c r="C26" s="42"/>
+      <c r="D26" s="42"/>
+      <c r="E26" s="42"/>
+      <c r="F26" s="42"/>
     </row>
     <row r="29" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="31" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="32" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="1" t="s">
+    <row r="32" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="54" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="10" t="s">
+      <c r="A33" s="44" t="s">
         <v>109</v>
       </c>
-      <c r="B33" s="17" t="s">
+      <c r="B33" s="44" t="s">
         <v>110</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="C33" s="44" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="42" t="s">
         <v>93</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" s="42" t="s">
         <v>112</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="42" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="42" t="s">
         <v>99</v>
       </c>
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="42" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="42" t="s">
         <v>94</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="42" t="s">
         <v>116</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" s="42" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="42" t="s">
         <v>118</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="42" t="s">
         <v>119</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="42" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="42" t="s">
         <v>121</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="42" t="s">
         <v>122</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="42" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="29" t="s">
+      <c r="A39" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="B39" s="26" t="s">
+      <c r="B39" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="C39" s="27" t="s">
+      <c r="C39" s="39" t="s">
         <v>95</v>
       </c>
-      <c r="D39" s="27" t="s">
+      <c r="D39" s="39" t="s">
         <v>124</v>
       </c>
-      <c r="E39" s="27" t="s">
+      <c r="E39" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="F39" s="27" t="s">
+      <c r="F39" s="39" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="57" x14ac:dyDescent="0.3">
-      <c r="A40" s="30" t="s">
+      <c r="A40" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="B40" s="38" t="s">
+      <c r="B40" s="40" t="s">
         <v>99</v>
       </c>
-      <c r="C40" s="31" t="s">
+      <c r="C40" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="D40" s="31" t="s">
+      <c r="D40" s="41" t="s">
         <v>125</v>
       </c>
-      <c r="E40" s="31" t="s">
+      <c r="E40" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="F40" s="31" t="s">
+      <c r="F40" s="41" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="57" x14ac:dyDescent="0.3">
-      <c r="A41" s="29" t="s">
+      <c r="A41" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="B41" s="26" t="s">
+      <c r="B41" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="C41" s="27" t="s">
+      <c r="C41" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="D41" s="27" t="s">
+      <c r="D41" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="E41" s="27" t="s">
+      <c r="E41" s="39" t="s">
         <v>128</v>
       </c>
-      <c r="F41" s="27" t="s">
+      <c r="F41" s="39" t="s">
         <v>129</v>
       </c>
     </row>
@@ -2731,20 +3034,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="34" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="37" t="s">
         <v>131</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -2772,10 +3075,10 @@
       <c r="B6" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="D6" s="33" t="s">
+      <c r="D6" s="30" t="s">
         <v>188</v>
       </c>
     </row>
@@ -2786,10 +3089,10 @@
       <c r="B7" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="D7" s="33" t="s">
+      <c r="D7" s="30" t="s">
         <v>189</v>
       </c>
     </row>
@@ -2800,10 +3103,10 @@
       <c r="B8" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="D8" s="33" t="s">
+      <c r="D8" s="30" t="s">
         <v>144</v>
       </c>
     </row>
@@ -2814,10 +3117,10 @@
       <c r="B9" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="D9" s="30" t="s">
         <v>221</v>
       </c>
     </row>
@@ -2828,10 +3131,10 @@
       <c r="B10" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="D10" s="33" t="s">
+      <c r="D10" s="30" t="s">
         <v>222</v>
       </c>
     </row>
@@ -2861,10 +3164,10 @@
       <c r="B14" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="C14" s="32" t="s">
+      <c r="C14" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="D14" s="33" t="s">
+      <c r="D14" s="30" t="s">
         <v>190</v>
       </c>
     </row>
@@ -2875,10 +3178,10 @@
       <c r="B15" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="C15" s="32" t="s">
+      <c r="C15" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="D15" s="33" t="s">
+      <c r="D15" s="30" t="s">
         <v>191</v>
       </c>
     </row>
@@ -2889,10 +3192,10 @@
       <c r="B16" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="C16" s="32" t="s">
+      <c r="C16" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="D16" s="33" t="s">
+      <c r="D16" s="30" t="s">
         <v>154</v>
       </c>
     </row>
@@ -2903,10 +3206,10 @@
       <c r="B17" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="C17" s="32" t="s">
+      <c r="C17" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="D17" s="33" t="s">
+      <c r="D17" s="30" t="s">
         <v>156</v>
       </c>
     </row>
@@ -2917,10 +3220,10 @@
       <c r="B18" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="C18" s="32" t="s">
+      <c r="C18" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="D18" s="33" t="s">
+      <c r="D18" s="30" t="s">
         <v>158</v>
       </c>
     </row>
@@ -2967,13 +3270,13 @@
       <c r="A28" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B28" s="34" t="s">
+      <c r="B28" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="C28" s="34" t="s">
+      <c r="C28" s="31" t="s">
         <v>168</v>
       </c>
-      <c r="D28" s="33" t="s">
+      <c r="D28" s="30" t="s">
         <v>186</v>
       </c>
     </row>
@@ -2981,13 +3284,13 @@
       <c r="A29" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B29" s="34" t="s">
+      <c r="B29" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="C29" s="34" t="s">
+      <c r="C29" s="31" t="s">
         <v>170</v>
       </c>
-      <c r="D29" s="33" t="s">
+      <c r="D29" s="30" t="s">
         <v>171</v>
       </c>
     </row>
@@ -2995,13 +3298,13 @@
       <c r="A30" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="B30" s="34" t="s">
+      <c r="B30" s="31" t="s">
         <v>172</v>
       </c>
-      <c r="C30" s="34" t="s">
+      <c r="C30" s="31" t="s">
         <v>173</v>
       </c>
-      <c r="D30" s="33" t="s">
+      <c r="D30" s="30" t="s">
         <v>186</v>
       </c>
     </row>
@@ -3009,13 +3312,13 @@
       <c r="A31" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="B31" s="34" t="s">
+      <c r="B31" s="31" t="s">
         <v>174</v>
       </c>
-      <c r="C31" s="34" t="s">
+      <c r="C31" s="31" t="s">
         <v>175</v>
       </c>
-      <c r="D31" s="33" t="s">
+      <c r="D31" s="30" t="s">
         <v>176</v>
       </c>
     </row>
@@ -3023,13 +3326,13 @@
       <c r="A32" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B32" s="34" t="s">
+      <c r="B32" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="C32" s="34" t="s">
+      <c r="C32" s="31" t="s">
         <v>178</v>
       </c>
-      <c r="D32" s="33" t="s">
+      <c r="D32" s="30" t="s">
         <v>179</v>
       </c>
     </row>
@@ -3037,13 +3340,13 @@
       <c r="A33" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="B33" s="34" t="s">
+      <c r="B33" s="31" t="s">
         <v>180</v>
       </c>
-      <c r="C33" s="34" t="s">
+      <c r="C33" s="31" t="s">
         <v>181</v>
       </c>
-      <c r="D33" s="33" t="s">
+      <c r="D33" s="30" t="s">
         <v>182</v>
       </c>
     </row>
@@ -3051,13 +3354,13 @@
       <c r="A34" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="34" t="s">
+      <c r="B34" s="31" t="s">
         <v>183</v>
       </c>
-      <c r="C34" s="34" t="s">
+      <c r="C34" s="31" t="s">
         <v>184</v>
       </c>
-      <c r="D34" s="33" t="s">
+      <c r="D34" s="30" t="s">
         <v>185</v>
       </c>
     </row>

--- a/ai_logs/Nguyên_AI_Log.xlsx
+++ b/ai_logs/Nguyên_AI_Log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\SUM26\labl\Food_delivery\ai_logs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{203A5EE5-78E2-492A-AC69-3FEE70DDF38B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9FE173A-986D-48D9-9C90-0CD6F10773B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -1354,71 +1354,71 @@
     <xf numFmtId="0" fontId="17" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1734,14 +1734,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="52" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
     </row>
     <row r="3" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -1818,7 +1818,7 @@
         <v>59</v>
       </c>
       <c r="C13" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
@@ -1993,28 +1993,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
@@ -2544,474 +2544,474 @@
   <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12" style="43" customWidth="1"/>
-    <col min="2" max="2" width="22" style="43" customWidth="1"/>
-    <col min="3" max="6" width="30" style="43" customWidth="1"/>
-    <col min="7" max="16384" width="8.88671875" style="43"/>
+    <col min="1" max="1" width="12" style="39" customWidth="1"/>
+    <col min="2" max="2" width="22" style="39" customWidth="1"/>
+    <col min="3" max="6" width="30" style="39" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="39"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="55" t="s">
         <v>85</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="53" t="s">
         <v>86</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
     </row>
     <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="C3" s="50" t="s">
+      <c r="C3" s="43" t="s">
         <v>89</v>
       </c>
-      <c r="D3" s="50" t="s">
+      <c r="D3" s="43" t="s">
         <v>90</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="E3" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="F3" s="50" t="s">
+      <c r="F3" s="43" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="51" t="s">
+      <c r="A4" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="38" t="s">
+      <c r="B4" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="C4" s="39" t="s">
+      <c r="C4" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="39" t="s">
+      <c r="D4" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="E4" s="39" t="s">
+      <c r="E4" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="39" t="s">
+      <c r="F4" s="35" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="C5" s="41" t="s">
+      <c r="C5" s="37" t="s">
         <v>100</v>
       </c>
-      <c r="D5" s="41" t="s">
+      <c r="D5" s="37" t="s">
         <v>101</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="37" t="s">
         <v>102</v>
       </c>
-      <c r="F5" s="41" t="s">
+      <c r="F5" s="37" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="C6" s="39" t="s">
+      <c r="C6" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="D6" s="39" t="s">
+      <c r="D6" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="E6" s="39" t="s">
+      <c r="E6" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="F6" s="39" t="s">
+      <c r="F6" s="35" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="99" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="51" t="s">
+      <c r="A7" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="C7" s="39" t="s">
+      <c r="C7" s="35" t="s">
         <v>213</v>
       </c>
-      <c r="D7" s="39" t="s">
+      <c r="D7" s="35" t="s">
         <v>214</v>
       </c>
-      <c r="E7" s="39" t="s">
+      <c r="E7" s="35" t="s">
         <v>215</v>
       </c>
-      <c r="F7" s="39" t="s">
+      <c r="F7" s="35" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="148.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="52" t="s">
+      <c r="A8" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="40" t="s">
+      <c r="B8" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="37" t="s">
         <v>217</v>
       </c>
-      <c r="D8" s="41" t="s">
+      <c r="D8" s="37" t="s">
         <v>218</v>
       </c>
-      <c r="E8" s="41" t="s">
+      <c r="E8" s="37" t="s">
         <v>219</v>
       </c>
-      <c r="F8" s="41" t="s">
+      <c r="F8" s="37" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="127.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="51" t="s">
+      <c r="A9" s="44" t="s">
         <v>251</v>
       </c>
-      <c r="B9" s="38" t="s">
+      <c r="B9" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="C9" s="35" t="s">
         <v>260</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="E9" s="39" t="s">
+      <c r="E9" s="35" t="s">
         <v>258</v>
       </c>
-      <c r="F9" s="39" t="s">
+      <c r="F9" s="35" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="136.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="45" t="s">
         <v>252</v>
       </c>
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="37" t="s">
         <v>256</v>
       </c>
-      <c r="D10" s="41" t="s">
+      <c r="D10" s="37" t="s">
         <v>255</v>
       </c>
-      <c r="E10" s="41" t="s">
+      <c r="E10" s="37" t="s">
         <v>254</v>
       </c>
-      <c r="F10" s="41" t="s">
+      <c r="F10" s="37" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="133.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="55" t="s">
+      <c r="A11" s="48" t="s">
         <v>286</v>
       </c>
-      <c r="B11" s="56" t="s">
+      <c r="B11" s="49" t="s">
         <v>99</v>
       </c>
-      <c r="C11" s="53" t="s">
+      <c r="C11" s="46" t="s">
         <v>291</v>
       </c>
-      <c r="D11" s="53" t="s">
+      <c r="D11" s="46" t="s">
         <v>292</v>
       </c>
-      <c r="E11" s="53" t="s">
+      <c r="E11" s="46" t="s">
         <v>293</v>
       </c>
-      <c r="F11" s="53" t="s">
+      <c r="F11" s="46" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="141" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="55" t="s">
+      <c r="A12" s="48" t="s">
         <v>290</v>
       </c>
-      <c r="B12" s="56" t="s">
+      <c r="B12" s="49" t="s">
         <v>99</v>
       </c>
-      <c r="C12" s="53" t="s">
+      <c r="C12" s="46" t="s">
         <v>295</v>
       </c>
-      <c r="D12" s="53" t="s">
+      <c r="D12" s="46" t="s">
         <v>296</v>
       </c>
-      <c r="E12" s="53" t="s">
+      <c r="E12" s="46" t="s">
         <v>297</v>
       </c>
-      <c r="F12" s="53" t="s">
+      <c r="F12" s="46" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="42"/>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
+      <c r="A13" s="38"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
     </row>
     <row r="14" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="42"/>
-      <c r="B14" s="42"/>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
+      <c r="A14" s="38"/>
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38"/>
     </row>
     <row r="15" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="42"/>
-      <c r="B15" s="42"/>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
+      <c r="A15" s="38"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
     </row>
     <row r="16" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="42"/>
-      <c r="B16" s="42"/>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
+      <c r="A16" s="38"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="38"/>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38"/>
     </row>
     <row r="17" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="42"/>
-      <c r="B17" s="42"/>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
+      <c r="A17" s="38"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
     </row>
     <row r="18" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="42"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
+      <c r="A18" s="38"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
     </row>
     <row r="19" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="42"/>
-      <c r="B19" s="42"/>
-      <c r="C19" s="42"/>
-      <c r="D19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="42"/>
+      <c r="A19" s="38"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
     </row>
     <row r="20" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="42"/>
-      <c r="B20" s="42"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
-      <c r="E20" s="42"/>
-      <c r="F20" s="42"/>
+      <c r="A20" s="38"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="38"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38"/>
     </row>
     <row r="21" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="42"/>
-      <c r="B21" s="42"/>
-      <c r="C21" s="42"/>
-      <c r="D21" s="42"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="42"/>
+      <c r="A21" s="38"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="38"/>
+      <c r="E21" s="38"/>
+      <c r="F21" s="38"/>
     </row>
     <row r="22" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="42"/>
-      <c r="B22" s="42"/>
-      <c r="C22" s="42"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
+      <c r="A22" s="38"/>
+      <c r="B22" s="38"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="38"/>
+      <c r="E22" s="38"/>
+      <c r="F22" s="38"/>
     </row>
     <row r="23" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="42"/>
-      <c r="B23" s="42"/>
-      <c r="C23" s="42"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
+      <c r="A23" s="38"/>
+      <c r="B23" s="38"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="38"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="42"/>
-      <c r="B24" s="42"/>
-      <c r="C24" s="42"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="42"/>
+      <c r="A24" s="38"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="38"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="42"/>
-      <c r="B25" s="42"/>
-      <c r="C25" s="42"/>
-      <c r="D25" s="42"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="42"/>
+      <c r="A25" s="38"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="42"/>
-      <c r="B26" s="42"/>
-      <c r="C26" s="42"/>
-      <c r="D26" s="42"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="42"/>
+      <c r="A26" s="38"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38"/>
     </row>
     <row r="29" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="31" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="32" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="54" t="s">
+      <c r="A32" s="47" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="44" t="s">
+      <c r="A33" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="B33" s="44" t="s">
+      <c r="B33" s="40" t="s">
         <v>110</v>
       </c>
-      <c r="C33" s="44" t="s">
+      <c r="C33" s="40" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="42" t="s">
+      <c r="A34" s="38" t="s">
         <v>93</v>
       </c>
-      <c r="B34" s="42" t="s">
+      <c r="B34" s="38" t="s">
         <v>112</v>
       </c>
-      <c r="C34" s="42" t="s">
+      <c r="C34" s="38" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="42" t="s">
+      <c r="A35" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="B35" s="42" t="s">
+      <c r="B35" s="38" t="s">
         <v>114</v>
       </c>
-      <c r="C35" s="42" t="s">
+      <c r="C35" s="38" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="42" t="s">
+      <c r="A36" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="B36" s="42" t="s">
+      <c r="B36" s="38" t="s">
         <v>116</v>
       </c>
-      <c r="C36" s="42" t="s">
+      <c r="C36" s="38" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="42" t="s">
+      <c r="A37" s="38" t="s">
         <v>118</v>
       </c>
-      <c r="B37" s="42" t="s">
+      <c r="B37" s="38" t="s">
         <v>119</v>
       </c>
-      <c r="C37" s="42" t="s">
+      <c r="C37" s="38" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="42" t="s">
+      <c r="A38" s="38" t="s">
         <v>121</v>
       </c>
-      <c r="B38" s="42" t="s">
+      <c r="B38" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="C38" s="42" t="s">
+      <c r="C38" s="38" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="45.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="45" t="s">
+      <c r="A39" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="B39" s="38" t="s">
+      <c r="B39" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="C39" s="39" t="s">
+      <c r="C39" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="D39" s="39" t="s">
+      <c r="D39" s="35" t="s">
         <v>124</v>
       </c>
-      <c r="E39" s="39" t="s">
+      <c r="E39" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="F39" s="39" t="s">
+      <c r="F39" s="35" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="57" x14ac:dyDescent="0.3">
-      <c r="A40" s="46" t="s">
+      <c r="A40" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="B40" s="40" t="s">
+      <c r="B40" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="C40" s="41" t="s">
+      <c r="C40" s="37" t="s">
         <v>100</v>
       </c>
-      <c r="D40" s="41" t="s">
+      <c r="D40" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="E40" s="41" t="s">
+      <c r="E40" s="37" t="s">
         <v>102</v>
       </c>
-      <c r="F40" s="41" t="s">
+      <c r="F40" s="37" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="57" x14ac:dyDescent="0.3">
-      <c r="A41" s="45" t="s">
+      <c r="A41" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="B41" s="38" t="s">
+      <c r="B41" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="C41" s="39" t="s">
+      <c r="C41" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="D41" s="39" t="s">
+      <c r="D41" s="35" t="s">
         <v>127</v>
       </c>
-      <c r="E41" s="39" t="s">
+      <c r="E41" s="35" t="s">
         <v>128</v>
       </c>
-      <c r="F41" s="39" t="s">
+      <c r="F41" s="35" t="s">
         <v>129</v>
       </c>
     </row>
@@ -3034,20 +3034,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="52" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="56" t="s">
         <v>131</v>
       </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
     </row>
     <row r="4" spans="1:4" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
